--- a/al_test_inventory.xlsx
+++ b/al_test_inventory.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Run Info" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Detail'!$A$1:$H$324</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Detail'!$A$1:$H$182</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -503,7 +503,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H324"/>
+  <dimension ref="A1:H182"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="65" customWidth="1" min="1" max="1"/>
@@ -4011,22 +4011,22 @@
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>extensions/Zig365-Commercial-Real-Estate-Property-Management-Contracts-Tests/src/AlternateCostCodeTest.Codeunit.al</t>
+          <t>extensions/Zig365-Commercial-Real-Estate-Property-Management-Contracts-Tests/src/RentBrokerageParameterTest.Codeunit.al</t>
         </is>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>AlternateCostCodeTest</t>
+          <t>RentBrokerageParameterTest</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>50113</t>
+          <t>50108</t>
         </is>
       </c>
       <c r="D117" s="2" t="inlineStr">
         <is>
-          <t>WhenNoContractLineCostCodeIsDefinedForPropertyOwner_ExpectError</t>
+          <t>WhenLettableObjectTypeIsEmpty_ExpectError</t>
         </is>
       </c>
       <c r="E117" s="2" t="inlineStr"/>
@@ -4041,22 +4041,22 @@
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>extensions/Zig365-Commercial-Real-Estate-Property-Management-Contracts-Tests/src/AlternateCostCodeTest.Codeunit.al</t>
+          <t>extensions/Zig365-Commercial-Real-Estate-Property-Management-Contracts-Tests/src/RentBrokerageParameterTest.Codeunit.al</t>
         </is>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>AlternateCostCodeTest</t>
+          <t>RentBrokerageParameterTest</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>50113</t>
+          <t>50108</t>
         </is>
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>AllUniqueContractLineCostCodesAreCollectedPerPropertyOwner</t>
+          <t>WhenDeletingAndUsedOnActivePropManContractLine_ExpectError</t>
         </is>
       </c>
       <c r="E118" s="2" t="inlineStr"/>
@@ -4071,22 +4071,22 @@
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>extensions/Zig365-Commercial-Real-Estate-Property-Management-Contracts-Tests/src/ExpensesEntryTest.Codeunit.al</t>
+          <t>extensions/Zig365-Commercial-Real-Estate-Property-Management-Contracts-Tests/src/RentBrokerageParameterTest.Codeunit.al</t>
         </is>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>ExpensesEntryTest</t>
+          <t>RentBrokerageParameterTest</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>50114</t>
+          <t>50108</t>
         </is>
       </c>
       <c r="D119" s="2" t="inlineStr">
         <is>
-          <t>GenJnlLineWithCostCode_BlanketContractLineActiveWithCostCode_ExpectExpensesEntryIsUpdated</t>
+          <t>WhenDeletingAndUsedOnActivePMBlanketContractLine_ExpectError</t>
         </is>
       </c>
       <c r="E119" s="2" t="inlineStr"/>
@@ -4101,22 +4101,22 @@
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>extensions/Zig365-Commercial-Real-Estate-Property-Management-Contracts-Tests/src/ExpensesEntryTest.Codeunit.al</t>
+          <t>extensions/Zig365-Commercial-Real-Estate-Property-Management-Contracts-Tests/src/RentBrokerageParameterTest.Codeunit.al</t>
         </is>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>ExpensesEntryTest</t>
+          <t>RentBrokerageParameterTest</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>50114</t>
+          <t>50108</t>
         </is>
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>GenJnlLineWithCostCode_WhenBlanketContractLineCostCodeNotExists_ExpectError</t>
+          <t>WhenDeletingAndOnlyUsedOnEndedPropManContractLine_ExpectIsDeleted</t>
         </is>
       </c>
       <c r="E120" s="2" t="inlineStr"/>
@@ -4131,22 +4131,22 @@
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>extensions/Zig365-Commercial-Real-Estate-Property-Management-Contracts-Tests/src/ExpensesEntryTest.Codeunit.al</t>
+          <t>extensions/Zig365-Commercial-Real-Estate-Property-Management-Contracts-Tests/src/RentBrokerageParameterTest.Codeunit.al</t>
         </is>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>ExpensesEntryTest</t>
+          <t>RentBrokerageParameterTest</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>50114</t>
+          <t>50108</t>
         </is>
       </c>
       <c r="D121" s="2" t="inlineStr">
         <is>
-          <t>GenJnlLineWithCostCode_WhenContractLineActiveWithCostCode_ExpectExpensesEntryIsUpdated</t>
+          <t>WhenDeletingAndOnlyUsedOnEndedPMBlanketContractLine_ExpectIsDeleted</t>
         </is>
       </c>
       <c r="E121" s="2" t="inlineStr"/>
@@ -4161,22 +4161,22 @@
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>extensions/Zig365-Commercial-Real-Estate-Property-Management-Contracts-Tests/src/ExpensesEntryTest.Codeunit.al</t>
+          <t>extensions/Zig365-Commercial-Real-Estate-Property-Management-Contracts-Tests/src/AlternateCostCodeTest.Codeunit.al</t>
         </is>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>ExpensesEntryTest</t>
+          <t>AlternateCostCodeTest</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>50114</t>
+          <t>50113</t>
         </is>
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>GenJnlLineWithCostCodeAndOwnerStatementCluster_WhenContractLineActiveWithCostCode_ExpectExpensesEntryIsUpdated</t>
+          <t>WhenNoContractLineCostCodeIsDefinedForPropertyOwner_ExpectError</t>
         </is>
       </c>
       <c r="E122" s="2" t="inlineStr"/>
@@ -4191,22 +4191,22 @@
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>extensions/Zig365-Commercial-Real-Estate-Property-Management-Contracts-Tests/src/ExpensesEntryTest.Codeunit.al</t>
+          <t>extensions/Zig365-Commercial-Real-Estate-Property-Management-Contracts-Tests/src/AlternateCostCodeTest.Codeunit.al</t>
         </is>
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>ExpensesEntryTest</t>
+          <t>AlternateCostCodeTest</t>
         </is>
       </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
-          <t>50114</t>
+          <t>50113</t>
         </is>
       </c>
       <c r="D123" s="2" t="inlineStr">
         <is>
-          <t>GenJnlLineWithCostCodeAndTechnicalCluster_ExpectNoExpensesEntryCreated</t>
+          <t>AllUniqueContractLineCostCodesAreCollectedPerPropertyOwner</t>
         </is>
       </c>
       <c r="E123" s="2" t="inlineStr"/>
@@ -4221,22 +4221,22 @@
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>extensions/Zig365-Commercial-Real-Estate-Property-Management-Contracts-Tests/src/ExpensesEntryTest.Codeunit.al</t>
+          <t>extensions/Zig365-Commercial-Real-Estate-Property-Management-Contracts-Tests/src/AlternateCostCodeTest.Codeunit.al</t>
         </is>
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>ExpensesEntryTest</t>
+          <t>AlternateCostCodeTest</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>50114</t>
+          <t>50113</t>
         </is>
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t>GenJnlLineWithCostCode_WhenNoContractActive_ExpectError</t>
+          <t>WhenClearAlternateCostCode_ExpectAlternateDescriptionIsCleared</t>
         </is>
       </c>
       <c r="E124" s="2" t="inlineStr"/>
@@ -4251,22 +4251,22 @@
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>extensions/Zig365-Commercial-Real-Estate-Property-Management-Contracts-Tests/src/ExpensesEntryTest.Codeunit.al</t>
+          <t>extensions/Zig365-Commercial-Real-Estate-Property-Management-Contracts-Tests/src/AlternateCostCodeTest.Codeunit.al</t>
         </is>
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>ExpensesEntryTest</t>
+          <t>AlternateCostCodeTest</t>
         </is>
       </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
-          <t>50114</t>
+          <t>50113</t>
         </is>
       </c>
       <c r="D125" s="2" t="inlineStr">
         <is>
-          <t>GenJnlLineWithCostCodeAndOwnerStatementCluster_WhenNoContractActive_ExpectError</t>
+          <t>WhenAlternateDescriptionIsFilledInAndAlternateCostCodeIsBlank_ExpectError</t>
         </is>
       </c>
       <c r="E125" s="2" t="inlineStr"/>
@@ -4281,22 +4281,22 @@
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>extensions/Zig365-Commercial-Real-Estate-Property-Management-Contracts-Tests/src/ExpensesEntryTest.Codeunit.al</t>
+          <t>extensions/Zig365-Commercial-Real-Estate-Property-Management-Contracts-Tests/src/AlternateCostCodeTest.Codeunit.al</t>
         </is>
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>ExpensesEntryTest</t>
+          <t>AlternateCostCodeTest</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>50114</t>
+          <t>50113</t>
         </is>
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t>GenJnlLineWithCostCode_WhenNoContractLineActive_ExpectError</t>
+          <t>GenerateCaptionReturnsPropertyOwnerNameAndCostCode</t>
         </is>
       </c>
       <c r="E126" s="2" t="inlineStr"/>
@@ -4326,7 +4326,7 @@
       </c>
       <c r="D127" s="2" t="inlineStr">
         <is>
-          <t>WhenBlanketContractLineActiveWithCostCode_ExpectExpensesEntryIsUpdated</t>
+          <t>GenJnlLineWithCostCode_BlanketContractLineActiveWithCostCode_ExpectExpensesEntryIsUpdated</t>
         </is>
       </c>
       <c r="E127" s="2" t="inlineStr"/>
@@ -4356,7 +4356,7 @@
       </c>
       <c r="D128" s="2" t="inlineStr">
         <is>
-          <t>WhenBlanketContractLineActiveWithCostCodeAndOwnerStatementCluster_ExpectExpensesEntryIsUpdated</t>
+          <t>GenJnlLineWithCostCode_WhenBlanketContractLineCostCodeNotExists_ExpectError</t>
         </is>
       </c>
       <c r="E128" s="2" t="inlineStr"/>
@@ -4386,7 +4386,7 @@
       </c>
       <c r="D129" s="2" t="inlineStr">
         <is>
-          <t>WhenBlanketContractLineCostCodeNotExists_ExpectError</t>
+          <t>GenJnlLineWithCostCode_WhenContractLineActiveWithCostCode_ExpectExpensesEntryIsUpdated</t>
         </is>
       </c>
       <c r="E129" s="2" t="inlineStr"/>
@@ -4416,7 +4416,7 @@
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t>WhenContractLineActiveWithCostCode_ExpectExpensesEntryIsUpdated</t>
+          <t>GenJnlLineWithCostCodeAndOwnerStatementCluster_WhenContractLineActiveWithCostCode_ExpectExpensesEntryIsUpdated</t>
         </is>
       </c>
       <c r="E130" s="2" t="inlineStr"/>
@@ -4446,7 +4446,7 @@
       </c>
       <c r="D131" s="2" t="inlineStr">
         <is>
-          <t>WhenTechnicalCluster_ExpectNoExpensesEntryCreated</t>
+          <t>GenJnlLineWithCostCodeAndTechnicalCluster_ExpectNoExpensesEntryCreated</t>
         </is>
       </c>
       <c r="E131" s="2" t="inlineStr"/>
@@ -4476,7 +4476,7 @@
       </c>
       <c r="D132" s="2" t="inlineStr">
         <is>
-          <t>WhenContractLineCostCodeNotExists_ExpectError</t>
+          <t>GenJnlLineWithCostCode_WhenNoContractActive_ExpectError</t>
         </is>
       </c>
       <c r="E132" s="2" t="inlineStr"/>
@@ -4506,7 +4506,7 @@
       </c>
       <c r="D133" s="2" t="inlineStr">
         <is>
-          <t>WhenNoBlanketContractLineActive_ExpectError</t>
+          <t>GenJnlLineWithCostCodeAndOwnerStatementCluster_WhenNoContractActive_ExpectError</t>
         </is>
       </c>
       <c r="E133" s="2" t="inlineStr"/>
@@ -4536,7 +4536,7 @@
       </c>
       <c r="D134" s="2" t="inlineStr">
         <is>
-          <t>WhenNoContractActive_ExpectError</t>
+          <t>GenJnlLineWithCostCode_WhenNoContractLineActive_ExpectError</t>
         </is>
       </c>
       <c r="E134" s="2" t="inlineStr"/>
@@ -4566,7 +4566,7 @@
       </c>
       <c r="D135" s="2" t="inlineStr">
         <is>
-          <t>WhenNoContractActiveAndOwnerStatementCluster_ExpectError</t>
+          <t>WhenBlanketContractLineActiveWithCostCode_ExpectExpensesEntryIsUpdated</t>
         </is>
       </c>
       <c r="E135" s="2" t="inlineStr"/>
@@ -4596,7 +4596,7 @@
       </c>
       <c r="D136" s="2" t="inlineStr">
         <is>
-          <t>WhenNoContractLineActive_ExpectError</t>
+          <t>WhenBlanketContractLineActiveWithCostCodeAndOwnerStatementCluster_ExpectExpensesEntryIsUpdated</t>
         </is>
       </c>
       <c r="E136" s="2" t="inlineStr"/>
@@ -4611,22 +4611,22 @@
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>extensions/Zig365-Commercial-Real-Estate-Property-Management-Contracts-Tests/src/ContractLineCostCodeTest.Codeunit.al</t>
+          <t>extensions/Zig365-Commercial-Real-Estate-Property-Management-Contracts-Tests/src/ExpensesEntryTest.Codeunit.al</t>
         </is>
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>ContractLineCostCodeTest</t>
+          <t>ExpensesEntryTest</t>
         </is>
       </c>
       <c r="C137" s="2" t="inlineStr">
         <is>
-          <t>50126</t>
+          <t>50114</t>
         </is>
       </c>
       <c r="D137" s="2" t="inlineStr">
         <is>
-          <t>WhenAddSelectedCostCodes_CostCodesAreAddedToPropManContract</t>
+          <t>WhenBlanketContractLineCostCodeNotExists_ExpectError</t>
         </is>
       </c>
       <c r="E137" s="2" t="inlineStr"/>
@@ -4641,22 +4641,22 @@
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>extensions/Zig365-Commercial-Real-Estate-Property-Management-Contracts-Tests/src/ContractLineCostCodeTest.Codeunit.al</t>
+          <t>extensions/Zig365-Commercial-Real-Estate-Property-Management-Contracts-Tests/src/ExpensesEntryTest.Codeunit.al</t>
         </is>
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>ContractLineCostCodeTest</t>
+          <t>ExpensesEntryTest</t>
         </is>
       </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
-          <t>50126</t>
+          <t>50114</t>
         </is>
       </c>
       <c r="D138" s="2" t="inlineStr">
         <is>
-          <t>WhenAddSelectedCostCodes_CostCodesAreAddedToPMBlanketContract</t>
+          <t>WhenContractLineActiveWithCostCode_ExpectExpensesEntryIsUpdated</t>
         </is>
       </c>
       <c r="E138" s="2" t="inlineStr"/>
@@ -4671,22 +4671,22 @@
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>extensions/Zig365-Commercial-Real-Estate-Property-Management-Contracts-Tests/src/CreateOwnerStatementErrorMsgs.Codeunit.al</t>
+          <t>extensions/Zig365-Commercial-Real-Estate-Property-Management-Contracts-Tests/src/ExpensesEntryTest.Codeunit.al</t>
         </is>
       </c>
       <c r="B139" s="2" t="inlineStr">
         <is>
-          <t>CreateOwnerStatementErrorMsgs</t>
+          <t>ExpensesEntryTest</t>
         </is>
       </c>
       <c r="C139" s="2" t="inlineStr">
         <is>
-          <t>50119</t>
+          <t>50114</t>
         </is>
       </c>
       <c r="D139" s="2" t="inlineStr">
         <is>
-          <t>CheckPeriodToSettle_FutureMonthSelected</t>
+          <t>WhenTechnicalCluster_ExpectNoExpensesEntryCreated</t>
         </is>
       </c>
       <c r="E139" s="2" t="inlineStr"/>
@@ -4701,22 +4701,22 @@
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>extensions/Zig365-Commercial-Real-Estate-Property-Management-Contracts-Tests/src/CreateOwnerStatementErrorMsgs.Codeunit.al</t>
+          <t>extensions/Zig365-Commercial-Real-Estate-Property-Management-Contracts-Tests/src/ExpensesEntryTest.Codeunit.al</t>
         </is>
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>CreateOwnerStatementErrorMsgs</t>
+          <t>ExpensesEntryTest</t>
         </is>
       </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
-          <t>50119</t>
+          <t>50114</t>
         </is>
       </c>
       <c r="D140" s="2" t="inlineStr">
         <is>
-          <t>CheckPeriodToSettle_FutureYearSelected</t>
+          <t>WhenContractLineCostCodeNotExists_ExpectError</t>
         </is>
       </c>
       <c r="E140" s="2" t="inlineStr"/>
@@ -4731,22 +4731,22 @@
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>extensions/Zig365-Commercial-Real-Estate-Property-Management-Contracts-Tests/src/CreateOwnerStatementErrorMsgs.Codeunit.al</t>
+          <t>extensions/Zig365-Commercial-Real-Estate-Property-Management-Contracts-Tests/src/ExpensesEntryTest.Codeunit.al</t>
         </is>
       </c>
       <c r="B141" s="2" t="inlineStr">
         <is>
-          <t>CreateOwnerStatementErrorMsgs</t>
+          <t>ExpensesEntryTest</t>
         </is>
       </c>
       <c r="C141" s="2" t="inlineStr">
         <is>
-          <t>50119</t>
+          <t>50114</t>
         </is>
       </c>
       <c r="D141" s="2" t="inlineStr">
         <is>
-          <t>CheckPeriodToSettle_NoPeriodSpecified</t>
+          <t>WhenNoBlanketContractLineActive_ExpectError</t>
         </is>
       </c>
       <c r="E141" s="2" t="inlineStr"/>
@@ -4761,22 +4761,22 @@
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>extensions/Zig365-Commercial-Real-Estate-Property-Management-Contracts-Tests/src/PropManContrLineElementTest.Codeunit.al</t>
+          <t>extensions/Zig365-Commercial-Real-Estate-Property-Management-Contracts-Tests/src/ExpensesEntryTest.Codeunit.al</t>
         </is>
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>PropManContrLineElementTest</t>
+          <t>ExpensesEntryTest</t>
         </is>
       </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
-          <t>50105</t>
+          <t>50114</t>
         </is>
       </c>
       <c r="D142" s="2" t="inlineStr">
         <is>
-          <t>WhenElementIsEmpty_ExpectError</t>
+          <t>WhenNoContractActive_ExpectError</t>
         </is>
       </c>
       <c r="E142" s="2" t="inlineStr"/>
@@ -4791,22 +4791,22 @@
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
-          <t>extensions/Zig365-Commercial-Real-Estate-Property-Management-Contracts-Tests/src/PropManContrLineElementTest.Codeunit.al</t>
+          <t>extensions/Zig365-Commercial-Real-Estate-Property-Management-Contracts-Tests/src/ExpensesEntryTest.Codeunit.al</t>
         </is>
       </c>
       <c r="B143" s="2" t="inlineStr">
         <is>
-          <t>PropManContrLineElementTest</t>
+          <t>ExpensesEntryTest</t>
         </is>
       </c>
       <c r="C143" s="2" t="inlineStr">
         <is>
-          <t>50105</t>
+          <t>50114</t>
         </is>
       </c>
       <c r="D143" s="2" t="inlineStr">
         <is>
-          <t>WhenPropManContrLineElementsAreCreated_CommissionAmountsAreCalculatedCorrectly</t>
+          <t>WhenNoContractActiveAndOwnerStatementCluster_ExpectError</t>
         </is>
       </c>
       <c r="E143" s="2" t="inlineStr"/>
@@ -4821,22 +4821,22 @@
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>extensions/Zig365-Commercial-Real-Estate-Property-Management-Contracts-Tests/src/PropManContrLineElementTest.Codeunit.al</t>
+          <t>extensions/Zig365-Commercial-Real-Estate-Property-Management-Contracts-Tests/src/ExpensesEntryTest.Codeunit.al</t>
         </is>
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>PropManContrLineElementTest</t>
+          <t>ExpensesEntryTest</t>
         </is>
       </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
-          <t>50105</t>
+          <t>50114</t>
         </is>
       </c>
       <c r="D144" s="2" t="inlineStr">
         <is>
-          <t>WhenAddSelectedElements_ElementsAreAdded</t>
+          <t>WhenNoContractLineActive_ExpectError</t>
         </is>
       </c>
       <c r="E144" s="2" t="inlineStr"/>
@@ -4851,22 +4851,22 @@
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
-          <t>extensions/Zig365-Commercial-Real-Estate-Property-Management-Contracts-Tests/src/PropManContractTest.Codeunit.al</t>
+          <t>extensions/Zig365-Commercial-Real-Estate-Property-Management-Contracts-Tests/src/ContractLineCostCodeTest.Codeunit.al</t>
         </is>
       </c>
       <c r="B145" s="2" t="inlineStr">
         <is>
-          <t>PropManContractTest</t>
+          <t>ContractLineCostCodeTest</t>
         </is>
       </c>
       <c r="C145" s="2" t="inlineStr">
         <is>
-          <t>50102</t>
+          <t>50126</t>
         </is>
       </c>
       <c r="D145" s="2" t="inlineStr">
         <is>
-          <t>WhenNoSeriesIsSetup_NoIsCorrectlyRetrieved</t>
+          <t>WhenAddSelectedCostCodes_CostCodesAreAddedToPropManContract</t>
         </is>
       </c>
       <c r="E145" s="2" t="inlineStr"/>
@@ -4881,22 +4881,22 @@
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>extensions/Zig365-Commercial-Real-Estate-Property-Management-Contracts-Tests/src/PropManContractTest.Codeunit.al</t>
+          <t>extensions/Zig365-Commercial-Real-Estate-Property-Management-Contracts-Tests/src/ContractLineCostCodeTest.Codeunit.al</t>
         </is>
       </c>
       <c r="B146" s="2" t="inlineStr">
         <is>
-          <t>PropManContractTest</t>
+          <t>ContractLineCostCodeTest</t>
         </is>
       </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
-          <t>50102</t>
+          <t>50126</t>
         </is>
       </c>
       <c r="D146" s="2" t="inlineStr">
         <is>
-          <t>WhenRelatedSeriesIsUsed_NoIsCorrectlyRetrieved</t>
+          <t>WhenAddSelectedCostCodes_CostCodesAreAddedToPMBlanketContract</t>
         </is>
       </c>
       <c r="E146" s="2" t="inlineStr"/>
@@ -4911,22 +4911,22 @@
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>extensions/Zig365-Commercial-Real-Estate-Property-Management-Contracts-Tests/src/PropManContractTest.Codeunit.al</t>
+          <t>extensions/Zig365-Commercial-Real-Estate-Property-Management-Contracts-Tests/src/CreateOwnerStatementErrorMsgs.Codeunit.al</t>
         </is>
       </c>
       <c r="B147" s="2" t="inlineStr">
         <is>
-          <t>PropManContractTest</t>
+          <t>CreateOwnerStatementErrorMsgs</t>
         </is>
       </c>
       <c r="C147" s="2" t="inlineStr">
         <is>
-          <t>50102</t>
+          <t>50119</t>
         </is>
       </c>
       <c r="D147" s="2" t="inlineStr">
         <is>
-          <t>WhenSetupDoesNotExist_ExpectError</t>
+          <t>CheckPeriodToSettle_FutureMonthSelected</t>
         </is>
       </c>
       <c r="E147" s="2" t="inlineStr"/>
@@ -4941,22 +4941,22 @@
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>extensions/Zig365-Commercial-Real-Estate-Property-Management-Contracts-Tests/src/PropManContractTest.Codeunit.al</t>
+          <t>extensions/Zig365-Commercial-Real-Estate-Property-Management-Contracts-Tests/src/CreateOwnerStatementErrorMsgs.Codeunit.al</t>
         </is>
       </c>
       <c r="B148" s="2" t="inlineStr">
         <is>
-          <t>PropManContractTest</t>
+          <t>CreateOwnerStatementErrorMsgs</t>
         </is>
       </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
-          <t>50102</t>
+          <t>50119</t>
         </is>
       </c>
       <c r="D148" s="2" t="inlineStr">
         <is>
-          <t>WhenNoSeriesIsNotSetup_ExpectError</t>
+          <t>CheckPeriodToSettle_FutureYearSelected</t>
         </is>
       </c>
       <c r="E148" s="2" t="inlineStr"/>
@@ -4971,22 +4971,22 @@
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
-          <t>extensions/Zig365-Commercial-Real-Estate-Property-Management-Contracts-Tests/src/PropManContractTest.Codeunit.al</t>
+          <t>extensions/Zig365-Commercial-Real-Estate-Property-Management-Contracts-Tests/src/CreateOwnerStatementErrorMsgs.Codeunit.al</t>
         </is>
       </c>
       <c r="B149" s="2" t="inlineStr">
         <is>
-          <t>PropManContractTest</t>
+          <t>CreateOwnerStatementErrorMsgs</t>
         </is>
       </c>
       <c r="C149" s="2" t="inlineStr">
         <is>
-          <t>50102</t>
+          <t>50119</t>
         </is>
       </c>
       <c r="D149" s="2" t="inlineStr">
         <is>
-          <t>WhenManualNosAreNotAccepted_ExpectError</t>
+          <t>CheckPeriodToSettle_NoPeriodSpecified</t>
         </is>
       </c>
       <c r="E149" s="2" t="inlineStr"/>
@@ -5001,22 +5001,22 @@
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>extensions/Zig365-Commercial-Real-Estate-Property-Management-Contracts-Tests/src/PropManContractTest.Codeunit.al</t>
+          <t>extensions/Zig365-Commercial-Real-Estate-Property-Management-Contracts-Tests/src/PropManContrLineElementTest.Codeunit.al</t>
         </is>
       </c>
       <c r="B150" s="2" t="inlineStr">
         <is>
-          <t>PropManContractTest</t>
+          <t>PropManContrLineElementTest</t>
         </is>
       </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
-          <t>50102</t>
+          <t>50105</t>
         </is>
       </c>
       <c r="D150" s="2" t="inlineStr">
         <is>
-          <t>WhenManualNosAreAccepted_ExpectNoCanBeAssigned</t>
+          <t>WhenElementIsEmpty_ExpectError</t>
         </is>
       </c>
       <c r="E150" s="2" t="inlineStr"/>
@@ -5031,22 +5031,22 @@
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
-          <t>extensions/Zig365-Commercial-Real-Estate-Property-Management-Contracts-Tests/src/PropManContractTest.Codeunit.al</t>
+          <t>extensions/Zig365-Commercial-Real-Estate-Property-Management-Contracts-Tests/src/PropManContrLineElementTest.Codeunit.al</t>
         </is>
       </c>
       <c r="B151" s="2" t="inlineStr">
         <is>
-          <t>PropManContractTest</t>
+          <t>PropManContrLineElementTest</t>
         </is>
       </c>
       <c r="C151" s="2" t="inlineStr">
         <is>
-          <t>50102</t>
+          <t>50105</t>
         </is>
       </c>
       <c r="D151" s="2" t="inlineStr">
         <is>
-          <t>WhenContractIsDeleted_PropertyOwnersAreDeleted</t>
+          <t>WhenPropManContrLineElementsAreCreated_CommissionAmountsAreCalculatedCorrectly</t>
         </is>
       </c>
       <c r="E151" s="2" t="inlineStr"/>
@@ -5061,22 +5061,22 @@
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
-          <t>extensions/Zig365-Commercial-Real-Estate-Property-Management-Contracts-Tests/src/PropManContractTest.Codeunit.al</t>
+          <t>extensions/Zig365-Commercial-Real-Estate-Property-Management-Contracts-Tests/src/PropManContrLineElementTest.Codeunit.al</t>
         </is>
       </c>
       <c r="B152" s="2" t="inlineStr">
         <is>
-          <t>PropManContractTest</t>
+          <t>PropManContrLineElementTest</t>
         </is>
       </c>
       <c r="C152" s="2" t="inlineStr">
         <is>
-          <t>50102</t>
+          <t>50105</t>
         </is>
       </c>
       <c r="D152" s="2" t="inlineStr">
         <is>
-          <t>WhenContractIsDeleted_ContractLinesAreDeleted</t>
+          <t>WhenAddSelectedElements_ElementsAreAdded</t>
         </is>
       </c>
       <c r="E152" s="2" t="inlineStr"/>
@@ -5106,7 +5106,7 @@
       </c>
       <c r="D153" s="2" t="inlineStr">
         <is>
-          <t>WhenClusterHasNotTheCorrectType_ExpectError</t>
+          <t>WhenNoSeriesIsSetup_NoIsCorrectlyRetrieved</t>
         </is>
       </c>
       <c r="E153" s="2" t="inlineStr"/>
@@ -5136,7 +5136,7 @@
       </c>
       <c r="D154" s="2" t="inlineStr">
         <is>
-          <t>WhenAddPropertyOwnerAndClusterIsEmpty_ExpectError</t>
+          <t>WhenRelatedSeriesIsUsed_NoIsCorrectlyRetrieved</t>
         </is>
       </c>
       <c r="E154" s="2" t="inlineStr"/>
@@ -5166,7 +5166,7 @@
       </c>
       <c r="D155" s="2" t="inlineStr">
         <is>
-          <t>WhenSetEndDateBeforeStartDate_ExpectError</t>
+          <t>WhenSetupDoesNotExist_ExpectError</t>
         </is>
       </c>
       <c r="E155" s="2" t="inlineStr"/>
@@ -5196,7 +5196,7 @@
       </c>
       <c r="D156" s="2" t="inlineStr">
         <is>
-          <t>WhenSetStartDateAfterEndDate_ExpectError</t>
+          <t>WhenNoSeriesIsNotSetup_ExpectError</t>
         </is>
       </c>
       <c r="E156" s="2" t="inlineStr"/>
@@ -5226,7 +5226,7 @@
       </c>
       <c r="D157" s="2" t="inlineStr">
         <is>
-          <t>WhenSetStartDateAndClusterIsEmpty_ExpectError</t>
+          <t>WhenManualNosAreNotAccepted_ExpectError</t>
         </is>
       </c>
       <c r="E157" s="2" t="inlineStr"/>
@@ -5256,7 +5256,7 @@
       </c>
       <c r="D158" s="2" t="inlineStr">
         <is>
-          <t>WhenSetStartDateAndContractLineWithLowerStartDateExists_ExpectError</t>
+          <t>WhenManualNosAreAccepted_ExpectNoCanBeAssigned</t>
         </is>
       </c>
       <c r="E158" s="2" t="inlineStr"/>
@@ -5286,7 +5286,7 @@
       </c>
       <c r="D159" s="2" t="inlineStr">
         <is>
-          <t>WhenClearStartDateAndContractLineExists_ExpectError</t>
+          <t>WhenContractIsDeleted_PropertyOwnersAreDeleted</t>
         </is>
       </c>
       <c r="E159" s="2" t="inlineStr"/>
@@ -5316,7 +5316,7 @@
       </c>
       <c r="D160" s="2" t="inlineStr">
         <is>
-          <t>WhenSetStartDateAndPreviousContractLineOverlappingExists_ExpectError</t>
+          <t>WhenContractIsDeleted_ContractLinesAreDeleted</t>
         </is>
       </c>
       <c r="E160" s="2" t="inlineStr"/>
@@ -5346,7 +5346,7 @@
       </c>
       <c r="D161" s="2" t="inlineStr">
         <is>
-          <t>WhenSetStartDateOnLineWithEndDateAndFutureContractLineOverlappingExists_ExpectError</t>
+          <t>WhenClusterHasNotTheCorrectType_ExpectError</t>
         </is>
       </c>
       <c r="E161" s="2" t="inlineStr"/>
@@ -5376,7 +5376,7 @@
       </c>
       <c r="D162" s="2" t="inlineStr">
         <is>
-          <t>WhenSetStartDateOnLineWithEmptyEndDateAndFutureContractLineOverlappingExists_ExpectError</t>
+          <t>WhenAddPropertyOwnerAndClusterIsEmpty_ExpectError</t>
         </is>
       </c>
       <c r="E162" s="2" t="inlineStr"/>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="D163" s="2" t="inlineStr">
         <is>
-          <t>WhenSetEndDateReceivingsExistAfterEndDate_ExpectError</t>
+          <t>WhenSetEndDateBeforeStartDate_ExpectError</t>
         </is>
       </c>
       <c r="E163" s="2" t="inlineStr"/>
@@ -5436,7 +5436,7 @@
       </c>
       <c r="D164" s="2" t="inlineStr">
         <is>
-          <t>WhenEndContractAndContractLineWithNewerStartDateExist_ExpectError</t>
+          <t>WhenSetStartDateAfterEndDate_ExpectError</t>
         </is>
       </c>
       <c r="E164" s="2" t="inlineStr"/>
@@ -5466,7 +5466,7 @@
       </c>
       <c r="D165" s="2" t="inlineStr">
         <is>
-          <t>WhenChangeExistingEndDateToNonEmptyValueAndOverlappingContractExists_ExpectError</t>
+          <t>WhenSetStartDateAndClusterIsEmpty_ExpectError</t>
         </is>
       </c>
       <c r="E165" s="2" t="inlineStr"/>
@@ -5496,7 +5496,7 @@
       </c>
       <c r="D166" s="2" t="inlineStr">
         <is>
-          <t>WhenChangeExistingEndDateToEmptyValueAndOverlappingContractExists_ExpectError</t>
+          <t>WhenSetStartDateAndContractLineWithLowerStartDateExists_ExpectError</t>
         </is>
       </c>
       <c r="E166" s="2" t="inlineStr"/>
@@ -5526,7 +5526,7 @@
       </c>
       <c r="D167" s="2" t="inlineStr">
         <is>
-          <t>WhenContractIsEnded_ExpectEndDateOnContractLineIsUpdated</t>
+          <t>WhenClearStartDateAndContractLineExists_ExpectError</t>
         </is>
       </c>
       <c r="E167" s="2" t="inlineStr"/>
@@ -5541,22 +5541,22 @@
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
-          <t>extensions/Zig365-Commercial-Real-Estate-Property-Management-Contracts-Tests/src/ReceivingsEntryTest.Codeunit.al</t>
+          <t>extensions/Zig365-Commercial-Real-Estate-Property-Management-Contracts-Tests/src/PropManContractTest.Codeunit.al</t>
         </is>
       </c>
       <c r="B168" s="2" t="inlineStr">
         <is>
-          <t>ReceivingsEntryTest</t>
+          <t>PropManContractTest</t>
         </is>
       </c>
       <c r="C168" s="2" t="inlineStr">
         <is>
-          <t>50112</t>
+          <t>50102</t>
         </is>
       </c>
       <c r="D168" s="2" t="inlineStr">
         <is>
-          <t>WhenNoContractLineActive_ExpectConcerningProlRunError</t>
+          <t>WhenSetStartDateAndPreviousContractLineOverlappingExists_ExpectError</t>
         </is>
       </c>
       <c r="E168" s="2" t="inlineStr"/>
@@ -5571,22 +5571,22 @@
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
-          <t>extensions/Zig365-Commercial-Real-Estate-Property-Management-Contracts-Tests/src/ReceivingsEntryTest.Codeunit.al</t>
+          <t>extensions/Zig365-Commercial-Real-Estate-Property-Management-Contracts-Tests/src/PropManContractTest.Codeunit.al</t>
         </is>
       </c>
       <c r="B169" s="2" t="inlineStr">
         <is>
-          <t>ReceivingsEntryTest</t>
+          <t>PropManContractTest</t>
         </is>
       </c>
       <c r="C169" s="2" t="inlineStr">
         <is>
-          <t>50112</t>
+          <t>50102</t>
         </is>
       </c>
       <c r="D169" s="2" t="inlineStr">
         <is>
-          <t>WhenNoContractLineElementRecorded_ExpectConcerningProlRunError</t>
+          <t>WhenSetStartDateOnLineWithEndDateAndFutureContractLineOverlappingExists_ExpectError</t>
         </is>
       </c>
       <c r="E169" s="2" t="inlineStr"/>
@@ -5601,22 +5601,22 @@
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
-          <t>extensions/Zig365-Commercial-Real-Estate-Property-Management-Contracts-Tests/src/ReceivingsEntryTest.Codeunit.al</t>
+          <t>extensions/Zig365-Commercial-Real-Estate-Property-Management-Contracts-Tests/src/PropManContractTest.Codeunit.al</t>
         </is>
       </c>
       <c r="B170" s="2" t="inlineStr">
         <is>
-          <t>ReceivingsEntryTest</t>
+          <t>PropManContractTest</t>
         </is>
       </c>
       <c r="C170" s="2" t="inlineStr">
         <is>
-          <t>50112</t>
+          <t>50102</t>
         </is>
       </c>
       <c r="D170" s="2" t="inlineStr">
         <is>
-          <t>WhenPMBlanketContractLineActive_ExpectContractNoUpdatedInReceivingsEntryAndRentalContract</t>
+          <t>WhenSetStartDateOnLineWithEmptyEndDateAndFutureContractLineOverlappingExists_ExpectError</t>
         </is>
       </c>
       <c r="E170" s="2" t="inlineStr"/>
@@ -5631,22 +5631,22 @@
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
         <is>
-          <t>extensions/Zig365-Commercial-Real-Estate-Property-Management-Contracts-Tests/src/ReceivingsEntryTest.Codeunit.al</t>
+          <t>extensions/Zig365-Commercial-Real-Estate-Property-Management-Contracts-Tests/src/PropManContractTest.Codeunit.al</t>
         </is>
       </c>
       <c r="B171" s="2" t="inlineStr">
         <is>
-          <t>ReceivingsEntryTest</t>
+          <t>PropManContractTest</t>
         </is>
       </c>
       <c r="C171" s="2" t="inlineStr">
         <is>
-          <t>50112</t>
+          <t>50102</t>
         </is>
       </c>
       <c r="D171" s="2" t="inlineStr">
         <is>
-          <t>WhenPostingRentalInvoice_ExpectContractNoUpdatedInReceivingsEntry</t>
+          <t>WhenSetEndDateReceivingsExistAfterEndDate_ExpectError</t>
         </is>
       </c>
       <c r="E171" s="2" t="inlineStr"/>
@@ -5661,22 +5661,22 @@
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
         <is>
-          <t>extensions/Zig365-Commercial-Real-Estate-Property-Management-Contracts-Tests/src/ReceivingsEntryTest.Codeunit.al</t>
+          <t>extensions/Zig365-Commercial-Real-Estate-Property-Management-Contracts-Tests/src/PropManContractTest.Codeunit.al</t>
         </is>
       </c>
       <c r="B172" s="2" t="inlineStr">
         <is>
-          <t>ReceivingsEntryTest</t>
+          <t>PropManContractTest</t>
         </is>
       </c>
       <c r="C172" s="2" t="inlineStr">
         <is>
-          <t>50112</t>
+          <t>50102</t>
         </is>
       </c>
       <c r="D172" s="2" t="inlineStr">
         <is>
-          <t>WhenPostingRentalInvoiceAndNoContractLineActive_ExpectConcerningError</t>
+          <t>WhenEndContractAndContractLineWithNewerStartDateExist_ExpectError</t>
         </is>
       </c>
       <c r="E172" s="2" t="inlineStr"/>
@@ -5691,22 +5691,22 @@
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
         <is>
-          <t>extensions/Zig365-Commercial-Real-Estate-Property-Management-Contracts-Tests/src/ReceivingsEntryTest.Codeunit.al</t>
+          <t>extensions/Zig365-Commercial-Real-Estate-Property-Management-Contracts-Tests/src/PropManContractTest.Codeunit.al</t>
         </is>
       </c>
       <c r="B173" s="2" t="inlineStr">
         <is>
-          <t>ReceivingsEntryTest</t>
+          <t>PropManContractTest</t>
         </is>
       </c>
       <c r="C173" s="2" t="inlineStr">
         <is>
-          <t>50112</t>
+          <t>50102</t>
         </is>
       </c>
       <c r="D173" s="2" t="inlineStr">
         <is>
-          <t>WhenPostingRentalInvoiceAndNoContractLineElementRecorded_ExpectConcerningError</t>
+          <t>WhenChangeExistingEndDateToNonEmptyValueAndOverlappingContractExists_ExpectError</t>
         </is>
       </c>
       <c r="E173" s="2" t="inlineStr"/>
@@ -5721,22 +5721,22 @@
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
         <is>
-          <t>extensions/Zig365-Commercial-Real-Estate-Property-Management-Contracts-Tests/src/ReceivingsEntryTest.Codeunit.al</t>
+          <t>extensions/Zig365-Commercial-Real-Estate-Property-Management-Contracts-Tests/src/PropManContractTest.Codeunit.al</t>
         </is>
       </c>
       <c r="B174" s="2" t="inlineStr">
         <is>
-          <t>ReceivingsEntryTest</t>
+          <t>PropManContractTest</t>
         </is>
       </c>
       <c r="C174" s="2" t="inlineStr">
         <is>
-          <t>50112</t>
+          <t>50102</t>
         </is>
       </c>
       <c r="D174" s="2" t="inlineStr">
         <is>
-          <t>WhenPropManContractLineActive_ExpectContractNoUpdatedInRentalContract</t>
+          <t>WhenChangeExistingEndDateToEmptyValueAndOverlappingContractExists_ExpectError</t>
         </is>
       </c>
       <c r="E174" s="2" t="inlineStr"/>
@@ -5751,22 +5751,22 @@
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
         <is>
-          <t>ERP.CRE/extensions/Zig365-Commercial-Real-Estate-Property-Management-Contracts-Tests/src/CreatePropManContractTest.Codeunit.al</t>
+          <t>extensions/Zig365-Commercial-Real-Estate-Property-Management-Contracts-Tests/src/PropManContractTest.Codeunit.al</t>
         </is>
       </c>
       <c r="B175" s="2" t="inlineStr">
         <is>
-          <t>CreatePropManContractTest</t>
+          <t>PropManContractTest</t>
         </is>
       </c>
       <c r="C175" s="2" t="inlineStr">
         <is>
-          <t>50110</t>
+          <t>50102</t>
         </is>
       </c>
       <c r="D175" s="2" t="inlineStr">
         <is>
-          <t>WhenPropertyOwnerIsEmpty_ExpectError</t>
+          <t>WhenContractIsEnded_ExpectEndDateOnContractLineIsUpdated</t>
         </is>
       </c>
       <c r="E175" s="2" t="inlineStr"/>
@@ -5781,22 +5781,22 @@
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
         <is>
-          <t>ERP.CRE/extensions/Zig365-Commercial-Real-Estate-Property-Management-Contracts-Tests/src/CreatePropManContractTest.Codeunit.al</t>
+          <t>extensions/Zig365-Commercial-Real-Estate-Property-Management-Contracts-Tests/src/ReceivingsEntryTest.Codeunit.al</t>
         </is>
       </c>
       <c r="B176" s="2" t="inlineStr">
         <is>
-          <t>CreatePropManContractTest</t>
+          <t>ReceivingsEntryTest</t>
         </is>
       </c>
       <c r="C176" s="2" t="inlineStr">
         <is>
-          <t>50110</t>
+          <t>50112</t>
         </is>
       </c>
       <c r="D176" s="2" t="inlineStr">
         <is>
-          <t>WhenNoPMBlanketContractLineExists_ExpectError</t>
+          <t>WhenNoContractLineActive_ExpectConcerningProlRunError</t>
         </is>
       </c>
       <c r="E176" s="2" t="inlineStr"/>
@@ -5811,4445 +5811,185 @@
     <row r="177">
       <c r="A177" s="2" t="inlineStr">
         <is>
-          <t>ERP.CRE/extensions/Zig365-Commercial-Real-Estate-Property-Management-Contracts-Tests/src/StatementCycleTest.Codeunit.al</t>
+          <t>extensions/Zig365-Commercial-Real-Estate-Property-Management-Contracts-Tests/src/ReceivingsEntryTest.Codeunit.al</t>
         </is>
       </c>
       <c r="B177" s="2" t="inlineStr">
         <is>
-          <t>StatementCycleTest</t>
+          <t>ReceivingsEntryTest</t>
         </is>
       </c>
       <c r="C177" s="2" t="inlineStr">
         <is>
-          <t>50117</t>
+          <t>50112</t>
         </is>
       </c>
       <c r="D177" s="2" t="inlineStr">
         <is>
-          <t>WhenDayNoIsHigherThan28AndUsedInClosingDateCalculation_ExpectError</t>
+          <t>WhenNoContractLineElementRecorded_ExpectConcerningProlRunError</t>
         </is>
       </c>
       <c r="E177" s="2" t="inlineStr"/>
       <c r="F177" s="2" t="inlineStr"/>
       <c r="G177" s="2" t="inlineStr"/>
-      <c r="H177" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="H177" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="2" t="inlineStr">
         <is>
-          <t>ERP.CRE/extensions/Zig365-Commercial-Real-Estate-Property-Management-Contracts-Tests/src/StatementCycleTest.Codeunit.al</t>
+          <t>extensions/Zig365-Commercial-Real-Estate-Property-Management-Contracts-Tests/src/ReceivingsEntryTest.Codeunit.al</t>
         </is>
       </c>
       <c r="B178" s="2" t="inlineStr">
         <is>
-          <t>StatementCycleTest</t>
+          <t>ReceivingsEntryTest</t>
         </is>
       </c>
       <c r="C178" s="2" t="inlineStr">
         <is>
-          <t>50117</t>
+          <t>50112</t>
         </is>
       </c>
       <c r="D178" s="2" t="inlineStr">
         <is>
-          <t>WhenDayNoIsInRange01Until28AndUsedInClosingDateCalculation_DoNotExpectError</t>
+          <t>WhenPMBlanketContractLineActive_ExpectContractNoUpdatedInReceivingsEntryAndRentalContract</t>
         </is>
       </c>
       <c r="E178" s="2" t="inlineStr"/>
       <c r="F178" s="2" t="inlineStr"/>
       <c r="G178" s="2" t="inlineStr"/>
-      <c r="H178" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="H178" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="2" t="inlineStr">
         <is>
-          <t>ERP.CRE/extensions/Zig365-Commercial-Real-Estate-Property-Management-Contracts-Tests/src/StatementCycleTest.Codeunit.al</t>
+          <t>extensions/Zig365-Commercial-Real-Estate-Property-Management-Contracts-Tests/src/ReceivingsEntryTest.Codeunit.al</t>
         </is>
       </c>
       <c r="B179" s="2" t="inlineStr">
         <is>
-          <t>StatementCycleTest</t>
+          <t>ReceivingsEntryTest</t>
         </is>
       </c>
       <c r="C179" s="2" t="inlineStr">
         <is>
-          <t>50117</t>
+          <t>50112</t>
         </is>
       </c>
       <c r="D179" s="2" t="inlineStr">
         <is>
-          <t>WhenExcludeCustomerFilterHasValueAndIncludeCustomerFilterIsEntered_ExpectError</t>
+          <t>WhenPostingRentalInvoice_ExpectContractNoUpdatedInReceivingsEntry</t>
         </is>
       </c>
       <c r="E179" s="2" t="inlineStr"/>
       <c r="F179" s="2" t="inlineStr"/>
       <c r="G179" s="2" t="inlineStr"/>
-      <c r="H179" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="H179" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="2" t="inlineStr">
         <is>
-          <t>ERP.CRE/extensions/Zig365-Commercial-Real-Estate-Property-Management-Contracts-Tests/src/StatementCycleTest.Codeunit.al</t>
+          <t>extensions/Zig365-Commercial-Real-Estate-Property-Management-Contracts-Tests/src/ReceivingsEntryTest.Codeunit.al</t>
         </is>
       </c>
       <c r="B180" s="2" t="inlineStr">
         <is>
-          <t>StatementCycleTest</t>
+          <t>ReceivingsEntryTest</t>
         </is>
       </c>
       <c r="C180" s="2" t="inlineStr">
         <is>
-          <t>50117</t>
+          <t>50112</t>
         </is>
       </c>
       <c r="D180" s="2" t="inlineStr">
         <is>
-          <t>WhenIncludeCustomerFilterHasValueAndExcludeCustomerFilterIsEntered_ExpectError</t>
+          <t>WhenPostingRentalInvoiceAndNoContractLineActive_ExpectConcerningError</t>
         </is>
       </c>
       <c r="E180" s="2" t="inlineStr"/>
       <c r="F180" s="2" t="inlineStr"/>
       <c r="G180" s="2" t="inlineStr"/>
-      <c r="H180" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="H180" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="2" t="inlineStr">
         <is>
-          <t>ERP.CRE/extensions/Zig365-Commercial-Real-Estate-Property-Management-Contracts-Tests/src/StatementCycleTest.Codeunit.al</t>
+          <t>extensions/Zig365-Commercial-Real-Estate-Property-Management-Contracts-Tests/src/ReceivingsEntryTest.Codeunit.al</t>
         </is>
       </c>
       <c r="B181" s="2" t="inlineStr">
         <is>
-          <t>StatementCycleTest</t>
+          <t>ReceivingsEntryTest</t>
         </is>
       </c>
       <c r="C181" s="2" t="inlineStr">
         <is>
-          <t>50117</t>
+          <t>50112</t>
         </is>
       </c>
       <c r="D181" s="2" t="inlineStr">
         <is>
-          <t>WhenPeriodNameIsEmpty_ExpectError</t>
+          <t>WhenPostingRentalInvoiceAndNoContractLineElementRecorded_ExpectConcerningError</t>
         </is>
       </c>
       <c r="E181" s="2" t="inlineStr"/>
       <c r="F181" s="2" t="inlineStr"/>
       <c r="G181" s="2" t="inlineStr"/>
-      <c r="H181" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="H181" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="2" t="inlineStr">
         <is>
-          <t>ERP.CRE/extensions/Zig365-Commercial-Real-Estate-Property-Management-Contracts-Tests/src/StatementCycleTest.Codeunit.al</t>
+          <t>extensions/Zig365-Commercial-Real-Estate-Property-Management-Contracts-Tests/src/ReceivingsEntryTest.Codeunit.al</t>
         </is>
       </c>
       <c r="B182" s="2" t="inlineStr">
         <is>
-          <t>StatementCycleTest</t>
+          <t>ReceivingsEntryTest</t>
         </is>
       </c>
       <c r="C182" s="2" t="inlineStr">
         <is>
-          <t>50117</t>
+          <t>50112</t>
         </is>
       </c>
       <c r="D182" s="2" t="inlineStr">
         <is>
-          <t>WhenPeriodNameIsNotEnteredViaLookup_ExpectError</t>
+          <t>WhenPropManContractLineActive_ExpectContractNoUpdatedInRentalContract</t>
         </is>
       </c>
       <c r="E182" s="2" t="inlineStr"/>
       <c r="F182" s="2" t="inlineStr"/>
       <c r="G182" s="2" t="inlineStr"/>
-      <c r="H182" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" s="2" t="inlineStr">
-        <is>
-          <t>ERP.CRE/extensions/Zig365-Commercial-Real-Estate-Property-Management-Contracts-Tests/src/StatementCycleTest.Codeunit.al</t>
-        </is>
-      </c>
-      <c r="B183" s="2" t="inlineStr">
-        <is>
-          <t>StatementCycleTest</t>
-        </is>
-      </c>
-      <c r="C183" s="2" t="inlineStr">
-        <is>
-          <t>50117</t>
-        </is>
-      </c>
-      <c r="D183" s="2" t="inlineStr">
-        <is>
-          <t>WhenStatementCycleIsDeleted_RelatedAlternateClosingDateIsAlsoDeleted</t>
-        </is>
-      </c>
-      <c r="E183" s="2" t="inlineStr"/>
-      <c r="F183" s="2" t="inlineStr"/>
-      <c r="G183" s="2" t="inlineStr"/>
-      <c r="H183" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" s="2" t="inlineStr">
-        <is>
-          <t>ERP.CRE/extensions/Zig365-Commercial-Real-Estate-Property-Management-Contracts-Tests/src/CommissionCalculationTest.Codeunit.al</t>
-        </is>
-      </c>
-      <c r="B184" s="2" t="inlineStr">
-        <is>
-          <t>CommissionCalculationTest</t>
-        </is>
-      </c>
-      <c r="C184" s="2" t="inlineStr">
-        <is>
-          <t>50121</t>
-        </is>
-      </c>
-      <c r="D184" s="2" t="inlineStr">
-        <is>
-          <t>VerifyCommissionCalculation</t>
-        </is>
-      </c>
-      <c r="E184" s="2" t="inlineStr"/>
-      <c r="F184" s="2" t="inlineStr"/>
-      <c r="G184" s="2" t="inlineStr"/>
-      <c r="H184" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" s="2" t="inlineStr">
-        <is>
-          <t>ERP.CRE/extensions/Zig365-Commercial-Real-Estate-Property-Management-Contracts-Tests/src/CustomerTest.Codeunit.al</t>
-        </is>
-      </c>
-      <c r="B185" s="2" t="inlineStr">
-        <is>
-          <t>CustomerTest</t>
-        </is>
-      </c>
-      <c r="C185" s="2" t="inlineStr">
-        <is>
-          <t>50111</t>
-        </is>
-      </c>
-      <c r="D185" s="2" t="inlineStr">
-        <is>
-          <t>WhenDeletingCustomerAndOpenPMBlanketContractExists_ExpectError</t>
-        </is>
-      </c>
-      <c r="E185" s="2" t="inlineStr"/>
-      <c r="F185" s="2" t="inlineStr"/>
-      <c r="G185" s="2" t="inlineStr"/>
-      <c r="H185" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" s="2" t="inlineStr">
-        <is>
-          <t>ERP.CRE/extensions/Zig365-Commercial-Real-Estate-Property-Management-Contracts-Tests/src/CustomerTest.Codeunit.al</t>
-        </is>
-      </c>
-      <c r="B186" s="2" t="inlineStr">
-        <is>
-          <t>CustomerTest</t>
-        </is>
-      </c>
-      <c r="C186" s="2" t="inlineStr">
-        <is>
-          <t>50111</t>
-        </is>
-      </c>
-      <c r="D186" s="2" t="inlineStr">
-        <is>
-          <t>WhenDeletingCustomerAndNoOpenPMBlanketContractExists_ExpectIsDeleted</t>
-        </is>
-      </c>
-      <c r="E186" s="2" t="inlineStr"/>
-      <c r="F186" s="2" t="inlineStr"/>
-      <c r="G186" s="2" t="inlineStr"/>
-      <c r="H186" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" s="2" t="inlineStr">
-        <is>
-          <t>ERP.CRE/extensions/Zig365-Commercial-Real-Estate-Property-Management-Contracts-Tests/src/CustomerTest.Codeunit.al</t>
-        </is>
-      </c>
-      <c r="B187" s="2" t="inlineStr">
-        <is>
-          <t>CustomerTest</t>
-        </is>
-      </c>
-      <c r="C187" s="2" t="inlineStr">
-        <is>
-          <t>50111</t>
-        </is>
-      </c>
-      <c r="D187" s="2" t="inlineStr">
-        <is>
-          <t>WhenDeletingCustomerAndOpenPropManContractExists_ExpectError</t>
-        </is>
-      </c>
-      <c r="E187" s="2" t="inlineStr"/>
-      <c r="F187" s="2" t="inlineStr"/>
-      <c r="G187" s="2" t="inlineStr"/>
-      <c r="H187" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" s="2" t="inlineStr">
-        <is>
-          <t>ERP.CRE/extensions/Zig365-Commercial-Real-Estate-Property-Management-Contracts-Tests/src/CustomerTest.Codeunit.al</t>
-        </is>
-      </c>
-      <c r="B188" s="2" t="inlineStr">
-        <is>
-          <t>CustomerTest</t>
-        </is>
-      </c>
-      <c r="C188" s="2" t="inlineStr">
-        <is>
-          <t>50111</t>
-        </is>
-      </c>
-      <c r="D188" s="2" t="inlineStr">
-        <is>
-          <t>WhenDeletingCustomerAndNoOpenPropManContractExists_ExpectIsDeleted</t>
-        </is>
-      </c>
-      <c r="E188" s="2" t="inlineStr"/>
-      <c r="F188" s="2" t="inlineStr"/>
-      <c r="G188" s="2" t="inlineStr"/>
-      <c r="H188" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" s="2" t="inlineStr">
-        <is>
-          <t>ERP.CRE/extensions/Zig365-Commercial-Real-Estate-Property-Management-Contracts-Tests/src/CustomerTest.Codeunit.al</t>
-        </is>
-      </c>
-      <c r="B189" s="2" t="inlineStr">
-        <is>
-          <t>CustomerTest</t>
-        </is>
-      </c>
-      <c r="C189" s="2" t="inlineStr">
-        <is>
-          <t>50111</t>
-        </is>
-      </c>
-      <c r="D189" s="2" t="inlineStr">
-        <is>
-          <t>WhenDeletingPropertyOwnerRelatedAlternateCostCodesAreDeleted</t>
-        </is>
-      </c>
-      <c r="E189" s="2" t="inlineStr"/>
-      <c r="F189" s="2" t="inlineStr"/>
-      <c r="G189" s="2" t="inlineStr"/>
-      <c r="H189" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190" s="2" t="inlineStr">
-        <is>
-          <t>ERP.CRE/extensions/Zig365-Commercial-Real-Estate-Property-Management-Contracts-Tests/src/PMBlanketContrLineElementTest.Codeunit.al</t>
-        </is>
-      </c>
-      <c r="B190" s="2" t="inlineStr">
-        <is>
-          <t>PMBlanketContrLineElementTest</t>
-        </is>
-      </c>
-      <c r="C190" s="2" t="inlineStr">
-        <is>
-          <t>50107</t>
-        </is>
-      </c>
-      <c r="D190" s="2" t="inlineStr">
-        <is>
-          <t>WhenElementIsEmpty_ExpectError</t>
-        </is>
-      </c>
-      <c r="E190" s="2" t="inlineStr"/>
-      <c r="F190" s="2" t="inlineStr"/>
-      <c r="G190" s="2" t="inlineStr"/>
-      <c r="H190" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="191">
-      <c r="A191" s="2" t="inlineStr">
-        <is>
-          <t>ERP.CRE/extensions/Zig365-Commercial-Real-Estate-Property-Management-Contracts-Tests/src/PMBlanketContrLineElementTest.Codeunit.al</t>
-        </is>
-      </c>
-      <c r="B191" s="2" t="inlineStr">
-        <is>
-          <t>PMBlanketContrLineElementTest</t>
-        </is>
-      </c>
-      <c r="C191" s="2" t="inlineStr">
-        <is>
-          <t>50107</t>
-        </is>
-      </c>
-      <c r="D191" s="2" t="inlineStr">
-        <is>
-          <t>WhenPMBlanketContractLineElementsAreCreated_CommissionAmountsAreCalculatedCorrectly</t>
-        </is>
-      </c>
-      <c r="E191" s="2" t="inlineStr"/>
-      <c r="F191" s="2" t="inlineStr"/>
-      <c r="G191" s="2" t="inlineStr"/>
-      <c r="H191" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" s="2" t="inlineStr">
-        <is>
-          <t>ERP.CRE/extensions/Zig365-Commercial-Real-Estate-Property-Management-Contracts-Tests/src/PMBlanketContrLineElementTest.Codeunit.al</t>
-        </is>
-      </c>
-      <c r="B192" s="2" t="inlineStr">
-        <is>
-          <t>PMBlanketContrLineElementTest</t>
-        </is>
-      </c>
-      <c r="C192" s="2" t="inlineStr">
-        <is>
-          <t>50107</t>
-        </is>
-      </c>
-      <c r="D192" s="2" t="inlineStr">
-        <is>
-          <t>WhenAddSelectedElements_ElementsAreAdded</t>
-        </is>
-      </c>
-      <c r="E192" s="2" t="inlineStr"/>
-      <c r="F192" s="2" t="inlineStr"/>
-      <c r="G192" s="2" t="inlineStr"/>
-      <c r="H192" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="193">
-      <c r="A193" s="2" t="inlineStr">
-        <is>
-          <t>ERP.CRE/extensions/Zig365-Commercial-Real-Estate-Property-Management-Contracts-Tests/src/ContractLineRentBrokerageTest.Codeunit.al</t>
-        </is>
-      </c>
-      <c r="B193" s="2" t="inlineStr">
-        <is>
-          <t>ContractLineRentBrokerageTest</t>
-        </is>
-      </c>
-      <c r="C193" s="2" t="inlineStr">
-        <is>
-          <t>50106</t>
-        </is>
-      </c>
-      <c r="D193" s="2" t="inlineStr">
-        <is>
-          <t>WhenAmountBasedOnIsChangedFromFixedAmountToBaseRent_ExpectAmountToBeZero</t>
-        </is>
-      </c>
-      <c r="E193" s="2" t="inlineStr"/>
-      <c r="F193" s="2" t="inlineStr"/>
-      <c r="G193" s="2" t="inlineStr"/>
-      <c r="H193" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" s="2" t="inlineStr">
-        <is>
-          <t>ERP.CRE/extensions/Zig365-Commercial-Real-Estate-Property-Management-Contracts-Tests/src/ContractLineRentBrokerageTest.Codeunit.al</t>
-        </is>
-      </c>
-      <c r="B194" s="2" t="inlineStr">
-        <is>
-          <t>ContractLineRentBrokerageTest</t>
-        </is>
-      </c>
-      <c r="C194" s="2" t="inlineStr">
-        <is>
-          <t>50106</t>
-        </is>
-      </c>
-      <c r="D194" s="2" t="inlineStr">
-        <is>
-          <t>WhenAmountBasedOnIsChangedFromBaseRentToFixedAmount_ExpectPercentageToBeZero</t>
-        </is>
-      </c>
-      <c r="E194" s="2" t="inlineStr"/>
-      <c r="F194" s="2" t="inlineStr"/>
-      <c r="G194" s="2" t="inlineStr"/>
-      <c r="H194" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="195">
-      <c r="A195" s="2" t="inlineStr">
-        <is>
-          <t>ERP.CRE/extensions/Zig365-Commercial-Real-Estate-Property-Management-Contracts-Tests/src/ProlChecksTest.Codeunit.al</t>
-        </is>
-      </c>
-      <c r="B195" s="2" t="inlineStr">
-        <is>
-          <t>ProlChecksTest</t>
-        </is>
-      </c>
-      <c r="C195" s="2" t="inlineStr">
-        <is>
-          <t>50127</t>
-        </is>
-      </c>
-      <c r="D195" s="2" t="inlineStr">
-        <is>
-          <t>WhenNoContractActive_ExpectConcerningProlRunError</t>
-        </is>
-      </c>
-      <c r="E195" s="2" t="inlineStr"/>
-      <c r="F195" s="2" t="inlineStr"/>
-      <c r="G195" s="2" t="inlineStr"/>
-      <c r="H195" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="196">
-      <c r="A196" s="2" t="inlineStr">
-        <is>
-          <t>ERP.CRE/extensions/Zig365-Commercial-Real-Estate-Property-Management-Contracts-Tests/src/ProlChecksTest.Codeunit.al</t>
-        </is>
-      </c>
-      <c r="B196" s="2" t="inlineStr">
-        <is>
-          <t>ProlChecksTest</t>
-        </is>
-      </c>
-      <c r="C196" s="2" t="inlineStr">
-        <is>
-          <t>50127</t>
-        </is>
-      </c>
-      <c r="D196" s="2" t="inlineStr">
-        <is>
-          <t>WhenNoPMBlanketContractLineActive_ExpectConcerningProlRunError</t>
-        </is>
-      </c>
-      <c r="E196" s="2" t="inlineStr"/>
-      <c r="F196" s="2" t="inlineStr"/>
-      <c r="G196" s="2" t="inlineStr"/>
-      <c r="H196" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" s="2" t="inlineStr">
-        <is>
-          <t>ERP.CRE/extensions/Zig365-Commercial-Real-Estate-Property-Management-Contracts-Tests/src/ProlChecksTest.Codeunit.al</t>
-        </is>
-      </c>
-      <c r="B197" s="2" t="inlineStr">
-        <is>
-          <t>ProlChecksTest</t>
-        </is>
-      </c>
-      <c r="C197" s="2" t="inlineStr">
-        <is>
-          <t>50127</t>
-        </is>
-      </c>
-      <c r="D197" s="2" t="inlineStr">
-        <is>
-          <t>WhenNoPMBlanketContractLineElementRecorded_ExpectConcerningProlRunError</t>
-        </is>
-      </c>
-      <c r="E197" s="2" t="inlineStr"/>
-      <c r="F197" s="2" t="inlineStr"/>
-      <c r="G197" s="2" t="inlineStr"/>
-      <c r="H197" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" s="2" t="inlineStr">
-        <is>
-          <t>ERP.CRE/extensions/Zig365-Commercial-Real-Estate-Property-Management-Contracts-Tests/src/ProlChecksTest.Codeunit.al</t>
-        </is>
-      </c>
-      <c r="B198" s="2" t="inlineStr">
-        <is>
-          <t>ProlChecksTest</t>
-        </is>
-      </c>
-      <c r="C198" s="2" t="inlineStr">
-        <is>
-          <t>50127</t>
-        </is>
-      </c>
-      <c r="D198" s="2" t="inlineStr">
-        <is>
-          <t>WhenNoPropManContractLineActive_ExpectConcerningProlRunError</t>
-        </is>
-      </c>
-      <c r="E198" s="2" t="inlineStr"/>
-      <c r="F198" s="2" t="inlineStr"/>
-      <c r="G198" s="2" t="inlineStr"/>
-      <c r="H198" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" s="2" t="inlineStr">
-        <is>
-          <t>ERP.CRE/extensions/Zig365-Commercial-Real-Estate-Property-Management-Contracts-Tests/src/ProlChecksTest.Codeunit.al</t>
-        </is>
-      </c>
-      <c r="B199" s="2" t="inlineStr">
-        <is>
-          <t>ProlChecksTest</t>
-        </is>
-      </c>
-      <c r="C199" s="2" t="inlineStr">
-        <is>
-          <t>50127</t>
-        </is>
-      </c>
-      <c r="D199" s="2" t="inlineStr">
-        <is>
-          <t>WhenNoPropManContractLineElementRecorded_ExpectConcerningProlRunError</t>
-        </is>
-      </c>
-      <c r="E199" s="2" t="inlineStr"/>
-      <c r="F199" s="2" t="inlineStr"/>
-      <c r="G199" s="2" t="inlineStr"/>
-      <c r="H199" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="200">
-      <c r="A200" s="2" t="inlineStr">
-        <is>
-          <t>ERP.CRE/extensions/Zig365-Commercial-Real-Estate-Property-Management-Contracts-Tests/src/ProlChecksTest.Codeunit.al</t>
-        </is>
-      </c>
-      <c r="B200" s="2" t="inlineStr">
-        <is>
-          <t>ProlChecksTest</t>
-        </is>
-      </c>
-      <c r="C200" s="2" t="inlineStr">
-        <is>
-          <t>50127</t>
-        </is>
-      </c>
-      <c r="D200" s="2" t="inlineStr">
-        <is>
-          <t>WhenPMBlanketContractLineElementRecorded_ExpectUpdatedRentalContractElement</t>
-        </is>
-      </c>
-      <c r="E200" s="2" t="inlineStr"/>
-      <c r="F200" s="2" t="inlineStr"/>
-      <c r="G200" s="2" t="inlineStr"/>
-      <c r="H200" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="201">
-      <c r="A201" s="2" t="inlineStr">
-        <is>
-          <t>ERP.CRE/extensions/Zig365-Commercial-Real-Estate-Property-Management-Contracts-Tests/src/ProlChecksTest.Codeunit.al</t>
-        </is>
-      </c>
-      <c r="B201" s="2" t="inlineStr">
-        <is>
-          <t>ProlChecksTest</t>
-        </is>
-      </c>
-      <c r="C201" s="2" t="inlineStr">
-        <is>
-          <t>50127</t>
-        </is>
-      </c>
-      <c r="D201" s="2" t="inlineStr">
-        <is>
-          <t>WhenPropManContractLineElementRecorded_ExpectUpdatedRentalContractElement</t>
-        </is>
-      </c>
-      <c r="E201" s="2" t="inlineStr"/>
-      <c r="F201" s="2" t="inlineStr"/>
-      <c r="G201" s="2" t="inlineStr"/>
-      <c r="H201" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="202">
-      <c r="A202" s="2" t="inlineStr">
-        <is>
-          <t>ERP.CRE/extensions/Zig365-Commercial-Real-Estate-Property-Management-Contracts-Tests/src/ProlChecksTest.Codeunit.al</t>
-        </is>
-      </c>
-      <c r="B202" s="2" t="inlineStr">
-        <is>
-          <t>ProlChecksTest</t>
-        </is>
-      </c>
-      <c r="C202" s="2" t="inlineStr">
-        <is>
-          <t>50127</t>
-        </is>
-      </c>
-      <c r="D202" s="2" t="inlineStr">
-        <is>
-          <t>WhenRentalContractIsInserted_PropertyOwnerRelatedFieldsAreCleared</t>
-        </is>
-      </c>
-      <c r="E202" s="2" t="inlineStr"/>
-      <c r="F202" s="2" t="inlineStr"/>
-      <c r="G202" s="2" t="inlineStr"/>
-      <c r="H202" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="203">
-      <c r="A203" s="2" t="inlineStr">
-        <is>
-          <t>ERP.CRE/extensions/Zig365-Commercial-Real-Estate-Property-Management-Contracts-Tests/src/PMBlanketContractTest.Codeunit.al</t>
-        </is>
-      </c>
-      <c r="B203" s="2" t="inlineStr">
-        <is>
-          <t>PMBlanketContractTest</t>
-        </is>
-      </c>
-      <c r="C203" s="2" t="inlineStr">
-        <is>
-          <t>50104</t>
-        </is>
-      </c>
-      <c r="D203" s="2" t="inlineStr">
-        <is>
-          <t>WhenNoSeriesIsSetup_NoIsCorrectlyRetrieved</t>
-        </is>
-      </c>
-      <c r="E203" s="2" t="inlineStr"/>
-      <c r="F203" s="2" t="inlineStr"/>
-      <c r="G203" s="2" t="inlineStr"/>
-      <c r="H203" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="204">
-      <c r="A204" s="2" t="inlineStr">
-        <is>
-          <t>ERP.CRE/extensions/Zig365-Commercial-Real-Estate-Property-Management-Contracts-Tests/src/PMBlanketContractTest.Codeunit.al</t>
-        </is>
-      </c>
-      <c r="B204" s="2" t="inlineStr">
-        <is>
-          <t>PMBlanketContractTest</t>
-        </is>
-      </c>
-      <c r="C204" s="2" t="inlineStr">
-        <is>
-          <t>50104</t>
-        </is>
-      </c>
-      <c r="D204" s="2" t="inlineStr">
-        <is>
-          <t>WhenRelatedSeriesIsUsed_NoIsCorrectlyRetrieved</t>
-        </is>
-      </c>
-      <c r="E204" s="2" t="inlineStr"/>
-      <c r="F204" s="2" t="inlineStr"/>
-      <c r="G204" s="2" t="inlineStr"/>
-      <c r="H204" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="205">
-      <c r="A205" s="2" t="inlineStr">
-        <is>
-          <t>ERP.CRE/extensions/Zig365-Commercial-Real-Estate-Property-Management-Contracts-Tests/src/PMBlanketContractTest.Codeunit.al</t>
-        </is>
-      </c>
-      <c r="B205" s="2" t="inlineStr">
-        <is>
-          <t>PMBlanketContractTest</t>
-        </is>
-      </c>
-      <c r="C205" s="2" t="inlineStr">
-        <is>
-          <t>50104</t>
-        </is>
-      </c>
-      <c r="D205" s="2" t="inlineStr">
-        <is>
-          <t>WhenSetupDoesNotExist_ExpectError</t>
-        </is>
-      </c>
-      <c r="E205" s="2" t="inlineStr"/>
-      <c r="F205" s="2" t="inlineStr"/>
-      <c r="G205" s="2" t="inlineStr"/>
-      <c r="H205" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="206">
-      <c r="A206" s="2" t="inlineStr">
-        <is>
-          <t>ERP.CRE/extensions/Zig365-Commercial-Real-Estate-Property-Management-Contracts-Tests/src/PMBlanketContractTest.Codeunit.al</t>
-        </is>
-      </c>
-      <c r="B206" s="2" t="inlineStr">
-        <is>
-          <t>PMBlanketContractTest</t>
-        </is>
-      </c>
-      <c r="C206" s="2" t="inlineStr">
-        <is>
-          <t>50104</t>
-        </is>
-      </c>
-      <c r="D206" s="2" t="inlineStr">
-        <is>
-          <t>WhenNoSeriesIsNotSetup_ExpectError</t>
-        </is>
-      </c>
-      <c r="E206" s="2" t="inlineStr"/>
-      <c r="F206" s="2" t="inlineStr"/>
-      <c r="G206" s="2" t="inlineStr"/>
-      <c r="H206" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="207">
-      <c r="A207" s="2" t="inlineStr">
-        <is>
-          <t>ERP.CRE/extensions/Zig365-Commercial-Real-Estate-Property-Management-Contracts-Tests/src/PMBlanketContractTest.Codeunit.al</t>
-        </is>
-      </c>
-      <c r="B207" s="2" t="inlineStr">
-        <is>
-          <t>PMBlanketContractTest</t>
-        </is>
-      </c>
-      <c r="C207" s="2" t="inlineStr">
-        <is>
-          <t>50104</t>
-        </is>
-      </c>
-      <c r="D207" s="2" t="inlineStr">
-        <is>
-          <t>WhenManualNosAreNotAccepted_ExpectError</t>
-        </is>
-      </c>
-      <c r="E207" s="2" t="inlineStr"/>
-      <c r="F207" s="2" t="inlineStr"/>
-      <c r="G207" s="2" t="inlineStr"/>
-      <c r="H207" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="208">
-      <c r="A208" s="2" t="inlineStr">
-        <is>
-          <t>ERP.CRE/extensions/Zig365-Commercial-Real-Estate-Property-Management-Contracts-Tests/src/PMBlanketContractTest.Codeunit.al</t>
-        </is>
-      </c>
-      <c r="B208" s="2" t="inlineStr">
-        <is>
-          <t>PMBlanketContractTest</t>
-        </is>
-      </c>
-      <c r="C208" s="2" t="inlineStr">
-        <is>
-          <t>50104</t>
-        </is>
-      </c>
-      <c r="D208" s="2" t="inlineStr">
-        <is>
-          <t>WhenManualNosAreAccepted_ExpectNoCanBeAssigned</t>
-        </is>
-      </c>
-      <c r="E208" s="2" t="inlineStr"/>
-      <c r="F208" s="2" t="inlineStr"/>
-      <c r="G208" s="2" t="inlineStr"/>
-      <c r="H208" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="209">
-      <c r="A209" s="2" t="inlineStr">
-        <is>
-          <t>ERP.CRE/extensions/Zig365-Commercial-Real-Estate-Property-Management-Contracts-Tests/src/PMBlanketContractTest.Codeunit.al</t>
-        </is>
-      </c>
-      <c r="B209" s="2" t="inlineStr">
-        <is>
-          <t>PMBlanketContractTest</t>
-        </is>
-      </c>
-      <c r="C209" s="2" t="inlineStr">
-        <is>
-          <t>50104</t>
-        </is>
-      </c>
-      <c r="D209" s="2" t="inlineStr">
-        <is>
-          <t>WhenBlanketContractIsDeleted_ContractLinesAreDeleted</t>
-        </is>
-      </c>
-      <c r="E209" s="2" t="inlineStr"/>
-      <c r="F209" s="2" t="inlineStr"/>
-      <c r="G209" s="2" t="inlineStr"/>
-      <c r="H209" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="210">
-      <c r="A210" s="2" t="inlineStr">
-        <is>
-          <t>ERP.CRE/extensions/Zig365-Commercial-Real-Estate-Property-Management-Contracts-Tests/src/PMBlanketContractTest.Codeunit.al</t>
-        </is>
-      </c>
-      <c r="B210" s="2" t="inlineStr">
-        <is>
-          <t>PMBlanketContractTest</t>
-        </is>
-      </c>
-      <c r="C210" s="2" t="inlineStr">
-        <is>
-          <t>50104</t>
-        </is>
-      </c>
-      <c r="D210" s="2" t="inlineStr">
-        <is>
-          <t>WhenBlanketContractIsDeletedAndContractsExist_ExpectError</t>
-        </is>
-      </c>
-      <c r="E210" s="2" t="inlineStr"/>
-      <c r="F210" s="2" t="inlineStr"/>
-      <c r="G210" s="2" t="inlineStr"/>
-      <c r="H210" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="211">
-      <c r="A211" s="2" t="inlineStr">
-        <is>
-          <t>ERP.CRE/extensions/Zig365-Commercial-Real-Estate-Property-Management-Contracts-Tests/src/PMBlanketContractTest.Codeunit.al</t>
-        </is>
-      </c>
-      <c r="B211" s="2" t="inlineStr">
-        <is>
-          <t>PMBlanketContractTest</t>
-        </is>
-      </c>
-      <c r="C211" s="2" t="inlineStr">
-        <is>
-          <t>50104</t>
-        </is>
-      </c>
-      <c r="D211" s="2" t="inlineStr">
-        <is>
-          <t>WhenPropertyOwnerIsChangedAndContractsExist_ExpectError</t>
-        </is>
-      </c>
-      <c r="E211" s="2" t="inlineStr"/>
-      <c r="F211" s="2" t="inlineStr"/>
-      <c r="G211" s="2" t="inlineStr"/>
-      <c r="H211" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="212">
-      <c r="A212" s="2" t="inlineStr">
-        <is>
-          <t>ERP.CRE/extensions/Zig365-Commercial-Real-Estate-Property-Management-Contracts-Tests/src/PMBlanketContractLineTest.Codeunit.al</t>
-        </is>
-      </c>
-      <c r="B212" s="2" t="inlineStr">
-        <is>
-          <t>PMBlanketContractLineTest</t>
-        </is>
-      </c>
-      <c r="C212" s="2" t="inlineStr">
-        <is>
-          <t>50101</t>
-        </is>
-      </c>
-      <c r="D212" s="2" t="inlineStr">
-        <is>
-          <t>WhenInsertFirstLine_LineNoIsCorrectlyDetermined</t>
-        </is>
-      </c>
-      <c r="E212" s="2" t="inlineStr"/>
-      <c r="F212" s="2" t="inlineStr"/>
-      <c r="G212" s="2" t="inlineStr"/>
-      <c r="H212" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="213">
-      <c r="A213" s="2" t="inlineStr">
-        <is>
-          <t>ERP.CRE/extensions/Zig365-Commercial-Real-Estate-Property-Management-Contracts-Tests/src/PMBlanketContractLineTest.Codeunit.al</t>
-        </is>
-      </c>
-      <c r="B213" s="2" t="inlineStr">
-        <is>
-          <t>PMBlanketContractLineTest</t>
-        </is>
-      </c>
-      <c r="C213" s="2" t="inlineStr">
-        <is>
-          <t>50101</t>
-        </is>
-      </c>
-      <c r="D213" s="2" t="inlineStr">
-        <is>
-          <t>WhenInsertSecondLine_LineNoIsCorrectlyDetermined</t>
-        </is>
-      </c>
-      <c r="E213" s="2" t="inlineStr"/>
-      <c r="F213" s="2" t="inlineStr"/>
-      <c r="G213" s="2" t="inlineStr"/>
-      <c r="H213" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="214">
-      <c r="A214" s="2" t="inlineStr">
-        <is>
-          <t>ERP.CRE/extensions/Zig365-Commercial-Real-Estate-Property-Management-Contracts-Tests/src/PMBlanketContractLineTest.Codeunit.al</t>
-        </is>
-      </c>
-      <c r="B214" s="2" t="inlineStr">
-        <is>
-          <t>PMBlanketContractLineTest</t>
-        </is>
-      </c>
-      <c r="C214" s="2" t="inlineStr">
-        <is>
-          <t>50101</t>
-        </is>
-      </c>
-      <c r="D214" s="2" t="inlineStr">
-        <is>
-          <t>WhenStartDateIsEmpty_ExpectError</t>
-        </is>
-      </c>
-      <c r="E214" s="2" t="inlineStr"/>
-      <c r="F214" s="2" t="inlineStr"/>
-      <c r="G214" s="2" t="inlineStr"/>
-      <c r="H214" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="215">
-      <c r="A215" s="2" t="inlineStr">
-        <is>
-          <t>ERP.CRE/extensions/Zig365-Commercial-Real-Estate-Property-Management-Contracts-Tests/src/PMBlanketContractLineTest.Codeunit.al</t>
-        </is>
-      </c>
-      <c r="B215" s="2" t="inlineStr">
-        <is>
-          <t>PMBlanketContractLineTest</t>
-        </is>
-      </c>
-      <c r="C215" s="2" t="inlineStr">
-        <is>
-          <t>50101</t>
-        </is>
-      </c>
-      <c r="D215" s="2" t="inlineStr">
-        <is>
-          <t>WhenValidateStartDateAndDateAlreadyExist_ExpectError</t>
-        </is>
-      </c>
-      <c r="E215" s="2" t="inlineStr"/>
-      <c r="F215" s="2" t="inlineStr"/>
-      <c r="G215" s="2" t="inlineStr"/>
-      <c r="H215" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="216">
-      <c r="A216" s="2" t="inlineStr">
-        <is>
-          <t>ERP.CRE/extensions/Zig365-Commercial-Real-Estate-Property-Management-Contracts-Tests/src/PMBlanketContractLineTest.Codeunit.al</t>
-        </is>
-      </c>
-      <c r="B216" s="2" t="inlineStr">
-        <is>
-          <t>PMBlanketContractLineTest</t>
-        </is>
-      </c>
-      <c r="C216" s="2" t="inlineStr">
-        <is>
-          <t>50101</t>
-        </is>
-      </c>
-      <c r="D216" s="2" t="inlineStr">
-        <is>
-          <t>WhenBlanketContractLineIsDeleted_BlanketContractLineElementsAreDeleted</t>
-        </is>
-      </c>
-      <c r="E216" s="2" t="inlineStr"/>
-      <c r="F216" s="2" t="inlineStr"/>
-      <c r="G216" s="2" t="inlineStr"/>
-      <c r="H216" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="217">
-      <c r="A217" s="2" t="inlineStr">
-        <is>
-          <t>ERP.CRE/extensions/Zig365-Commercial-Real-Estate-Property-Management-Contracts-Tests/src/PMBlanketContractLineTest.Codeunit.al</t>
-        </is>
-      </c>
-      <c r="B217" s="2" t="inlineStr">
-        <is>
-          <t>PMBlanketContractLineTest</t>
-        </is>
-      </c>
-      <c r="C217" s="2" t="inlineStr">
-        <is>
-          <t>50101</t>
-        </is>
-      </c>
-      <c r="D217" s="2" t="inlineStr">
-        <is>
-          <t>WhenBlanketContractLineIsDeleted_BlanketContractLineLettableObjTypesAreDeleted</t>
-        </is>
-      </c>
-      <c r="E217" s="2" t="inlineStr"/>
-      <c r="F217" s="2" t="inlineStr"/>
-      <c r="G217" s="2" t="inlineStr"/>
-      <c r="H217" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="218">
-      <c r="A218" s="2" t="inlineStr">
-        <is>
-          <t>ERP.CRE/extensions/Zig365-Commercial-Real-Estate-Property-Management-Contracts-Tests/src/PMBlanketContractLineTest.Codeunit.al</t>
-        </is>
-      </c>
-      <c r="B218" s="2" t="inlineStr">
-        <is>
-          <t>PMBlanketContractLineTest</t>
-        </is>
-      </c>
-      <c r="C218" s="2" t="inlineStr">
-        <is>
-          <t>50101</t>
-        </is>
-      </c>
-      <c r="D218" s="2" t="inlineStr">
-        <is>
-          <t>WhenBlanketContractLineIsDeleted_BlanketContractLineCostCodesAreDeleted</t>
-        </is>
-      </c>
-      <c r="E218" s="2" t="inlineStr"/>
-      <c r="F218" s="2" t="inlineStr"/>
-      <c r="G218" s="2" t="inlineStr"/>
-      <c r="H218" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="219">
-      <c r="A219" s="2" t="inlineStr">
-        <is>
-          <t>ERP.CRE/extensions/Zig365-Commercial-Real-Estate-Property-Management-Contracts-Tests/src/PMBlanketContractLineTest.Codeunit.al</t>
-        </is>
-      </c>
-      <c r="B219" s="2" t="inlineStr">
-        <is>
-          <t>PMBlanketContractLineTest</t>
-        </is>
-      </c>
-      <c r="C219" s="2" t="inlineStr">
-        <is>
-          <t>50101</t>
-        </is>
-      </c>
-      <c r="D219" s="2" t="inlineStr">
-        <is>
-          <t>WhenBlanketContractLineIsDeleted_BlanketContractLineRentBrokeragesAreDeleted</t>
-        </is>
-      </c>
-      <c r="E219" s="2" t="inlineStr"/>
-      <c r="F219" s="2" t="inlineStr"/>
-      <c r="G219" s="2" t="inlineStr"/>
-      <c r="H219" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="220">
-      <c r="A220" s="2" t="inlineStr">
-        <is>
-          <t>ERP.CRE/extensions/Zig365-Commercial-Real-Estate-Property-Management-Contracts-Tests/src/PMBlanketContractLineTest.Codeunit.al</t>
-        </is>
-      </c>
-      <c r="B220" s="2" t="inlineStr">
-        <is>
-          <t>PMBlanketContractLineTest</t>
-        </is>
-      </c>
-      <c r="C220" s="2" t="inlineStr">
-        <is>
-          <t>50101</t>
-        </is>
-      </c>
-      <c r="D220" s="2" t="inlineStr">
-        <is>
-          <t>WhenBlanketContractLineIsDeleted_BlanketContractLineFeesAreDeleted</t>
-        </is>
-      </c>
-      <c r="E220" s="2" t="inlineStr"/>
-      <c r="F220" s="2" t="inlineStr"/>
-      <c r="G220" s="2" t="inlineStr"/>
-      <c r="H220" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="221">
-      <c r="A221" s="2" t="inlineStr">
-        <is>
-          <t>ERP.CRE/extensions/Zig365-Commercial-Real-Estate-Property-Management-Contracts-Tests/src/PMBlanketContractLineTest.Codeunit.al</t>
-        </is>
-      </c>
-      <c r="B221" s="2" t="inlineStr">
-        <is>
-          <t>PMBlanketContractLineTest</t>
-        </is>
-      </c>
-      <c r="C221" s="2" t="inlineStr">
-        <is>
-          <t>50101</t>
-        </is>
-      </c>
-      <c r="D221" s="2" t="inlineStr">
-        <is>
-          <t>WhenInsertNewLineWithStartDateAfterExistingLine_ExpectEndDateIsUpdatedOnPreviousLine</t>
-        </is>
-      </c>
-      <c r="E221" s="2" t="inlineStr"/>
-      <c r="F221" s="2" t="inlineStr"/>
-      <c r="G221" s="2" t="inlineStr"/>
-      <c r="H221" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="222">
-      <c r="A222" s="2" t="inlineStr">
-        <is>
-          <t>ERP.CRE/extensions/Zig365-Commercial-Real-Estate-Property-Management-Contracts-Tests/src/PMBlanketContractLineTest.Codeunit.al</t>
-        </is>
-      </c>
-      <c r="B222" s="2" t="inlineStr">
-        <is>
-          <t>PMBlanketContractLineTest</t>
-        </is>
-      </c>
-      <c r="C222" s="2" t="inlineStr">
-        <is>
-          <t>50101</t>
-        </is>
-      </c>
-      <c r="D222" s="2" t="inlineStr">
-        <is>
-          <t>WhenInsertNewLineWithStartDateBeforeExistingLine_ExpectEndDateIsUpdated</t>
-        </is>
-      </c>
-      <c r="E222" s="2" t="inlineStr"/>
-      <c r="F222" s="2" t="inlineStr"/>
-      <c r="G222" s="2" t="inlineStr"/>
-      <c r="H222" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="223">
-      <c r="A223" s="2" t="inlineStr">
-        <is>
-          <t>ERP.CRE/extensions/Zig365-Commercial-Real-Estate-Property-Management-Contracts-Tests/src/PMBlanketContractLineTest.Codeunit.al</t>
-        </is>
-      </c>
-      <c r="B223" s="2" t="inlineStr">
-        <is>
-          <t>PMBlanketContractLineTest</t>
-        </is>
-      </c>
-      <c r="C223" s="2" t="inlineStr">
-        <is>
-          <t>50101</t>
-        </is>
-      </c>
-      <c r="D223" s="2" t="inlineStr">
-        <is>
-          <t>WhenInsertNewLineBetweenTwoLines_ExpectEndDateIsUpdatedOnCurrentAndPreviousLine</t>
-        </is>
-      </c>
-      <c r="E223" s="2" t="inlineStr"/>
-      <c r="F223" s="2" t="inlineStr"/>
-      <c r="G223" s="2" t="inlineStr"/>
-      <c r="H223" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="224">
-      <c r="A224" s="2" t="inlineStr">
-        <is>
-          <t>ERP.CRE/extensions/Zig365-Commercial-Real-Estate-Property-Management-Contracts-Tests/src/PMBlanketContractLineTest.Codeunit.al</t>
-        </is>
-      </c>
-      <c r="B224" s="2" t="inlineStr">
-        <is>
-          <t>PMBlanketContractLineTest</t>
-        </is>
-      </c>
-      <c r="C224" s="2" t="inlineStr">
-        <is>
-          <t>50101</t>
-        </is>
-      </c>
-      <c r="D224" s="2" t="inlineStr">
-        <is>
-          <t>WhenModifyStartDateLowerThanPreviousValue_ExpectEndDateIsUpdatedOnPreviousLine</t>
-        </is>
-      </c>
-      <c r="E224" s="2" t="inlineStr"/>
-      <c r="F224" s="2" t="inlineStr"/>
-      <c r="G224" s="2" t="inlineStr"/>
-      <c r="H224" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="225">
-      <c r="A225" s="2" t="inlineStr">
-        <is>
-          <t>ERP.CRE/extensions/Zig365-Commercial-Real-Estate-Property-Management-Contracts-Tests/src/PMBlanketContractLineTest.Codeunit.al</t>
-        </is>
-      </c>
-      <c r="B225" s="2" t="inlineStr">
-        <is>
-          <t>PMBlanketContractLineTest</t>
-        </is>
-      </c>
-      <c r="C225" s="2" t="inlineStr">
-        <is>
-          <t>50101</t>
-        </is>
-      </c>
-      <c r="D225" s="2" t="inlineStr">
-        <is>
-          <t>WhenModifyStartDateHigherThanPreviousValue_ExpectEndDateIsUpdatedOnPreviousLine</t>
-        </is>
-      </c>
-      <c r="E225" s="2" t="inlineStr"/>
-      <c r="F225" s="2" t="inlineStr"/>
-      <c r="G225" s="2" t="inlineStr"/>
-      <c r="H225" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="226">
-      <c r="A226" s="2" t="inlineStr">
-        <is>
-          <t>ERP.CRE/extensions/Zig365-Commercial-Real-Estate-Property-Management-Contracts-Tests/src/PMBlanketContractLineTest.Codeunit.al</t>
-        </is>
-      </c>
-      <c r="B226" s="2" t="inlineStr">
-        <is>
-          <t>PMBlanketContractLineTest</t>
-        </is>
-      </c>
-      <c r="C226" s="2" t="inlineStr">
-        <is>
-          <t>50101</t>
-        </is>
-      </c>
-      <c r="D226" s="2" t="inlineStr">
-        <is>
-          <t>WhenModifyStartDateLowerThanFirstLine_ExpectEndDateIsUpdatedOnAllLines</t>
-        </is>
-      </c>
-      <c r="E226" s="2" t="inlineStr"/>
-      <c r="F226" s="2" t="inlineStr"/>
-      <c r="G226" s="2" t="inlineStr"/>
-      <c r="H226" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="227">
-      <c r="A227" s="2" t="inlineStr">
-        <is>
-          <t>ERP.CRE/extensions/Zig365-Commercial-Real-Estate-Property-Management-Contracts-Tests/src/PMBlanketContractLineTest.Codeunit.al</t>
-        </is>
-      </c>
-      <c r="B227" s="2" t="inlineStr">
-        <is>
-          <t>PMBlanketContractLineTest</t>
-        </is>
-      </c>
-      <c r="C227" s="2" t="inlineStr">
-        <is>
-          <t>50101</t>
-        </is>
-      </c>
-      <c r="D227" s="2" t="inlineStr">
-        <is>
-          <t>WhenModifyStartDateHigherThanLastLine_ExpectEndDateIsUpdatedOnAllLines</t>
-        </is>
-      </c>
-      <c r="E227" s="2" t="inlineStr"/>
-      <c r="F227" s="2" t="inlineStr"/>
-      <c r="G227" s="2" t="inlineStr"/>
-      <c r="H227" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="228">
-      <c r="A228" s="2" t="inlineStr">
-        <is>
-          <t>ERP.CRE/extensions/Zig365-Commercial-Real-Estate-Property-Management-Contracts-Tests/src/PMBlanketContractLineTest.Codeunit.al</t>
-        </is>
-      </c>
-      <c r="B228" s="2" t="inlineStr">
-        <is>
-          <t>PMBlanketContractLineTest</t>
-        </is>
-      </c>
-      <c r="C228" s="2" t="inlineStr">
-        <is>
-          <t>50101</t>
-        </is>
-      </c>
-      <c r="D228" s="2" t="inlineStr">
-        <is>
-          <t>WhenModifyStartDateAndTheOrderRemainsTheSame_ExpectEndDateOnPreviousLineIsUpdated</t>
-        </is>
-      </c>
-      <c r="E228" s="2" t="inlineStr"/>
-      <c r="F228" s="2" t="inlineStr"/>
-      <c r="G228" s="2" t="inlineStr"/>
-      <c r="H228" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="229">
-      <c r="A229" s="2" t="inlineStr">
-        <is>
-          <t>ERP.CRE/extensions/Zig365-Commercial-Real-Estate-Property-Management-Contracts-Tests/src/PMBlanketContractLineTest.Codeunit.al</t>
-        </is>
-      </c>
-      <c r="B229" s="2" t="inlineStr">
-        <is>
-          <t>PMBlanketContractLineTest</t>
-        </is>
-      </c>
-      <c r="C229" s="2" t="inlineStr">
-        <is>
-          <t>50101</t>
-        </is>
-      </c>
-      <c r="D229" s="2" t="inlineStr">
-        <is>
-          <t>WhenDeleteLastLine_ExpectEndDateIsClearedOnPreviousLine</t>
-        </is>
-      </c>
-      <c r="E229" s="2" t="inlineStr"/>
-      <c r="F229" s="2" t="inlineStr"/>
-      <c r="G229" s="2" t="inlineStr"/>
-      <c r="H229" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="230">
-      <c r="A230" s="2" t="inlineStr">
-        <is>
-          <t>ERP.CRE/extensions/Zig365-Commercial-Real-Estate-Property-Management-Contracts-Tests/src/PMBlanketContractLineTest.Codeunit.al</t>
-        </is>
-      </c>
-      <c r="B230" s="2" t="inlineStr">
-        <is>
-          <t>PMBlanketContractLineTest</t>
-        </is>
-      </c>
-      <c r="C230" s="2" t="inlineStr">
-        <is>
-          <t>50101</t>
-        </is>
-      </c>
-      <c r="D230" s="2" t="inlineStr">
-        <is>
-          <t>WhenDeleteNextToLastLine_ExpectEndDateIsUpdatedOnPreviousLine</t>
-        </is>
-      </c>
-      <c r="E230" s="2" t="inlineStr"/>
-      <c r="F230" s="2" t="inlineStr"/>
-      <c r="G230" s="2" t="inlineStr"/>
-      <c r="H230" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="231">
-      <c r="A231" s="2" t="inlineStr">
-        <is>
-          <t>ERP.CRE/extensions/Zig365-Commercial-Real-Estate-Property-Management-Contracts-Tests/src/PMBlanketContractLineTest.Codeunit.al</t>
-        </is>
-      </c>
-      <c r="B231" s="2" t="inlineStr">
-        <is>
-          <t>PMBlanketContractLineTest</t>
-        </is>
-      </c>
-      <c r="C231" s="2" t="inlineStr">
-        <is>
-          <t>50101</t>
-        </is>
-      </c>
-      <c r="D231" s="2" t="inlineStr">
-        <is>
-          <t>WhenLettableObjectTypeIsEmpty_ExpectError</t>
-        </is>
-      </c>
-      <c r="E231" s="2" t="inlineStr"/>
-      <c r="F231" s="2" t="inlineStr"/>
-      <c r="G231" s="2" t="inlineStr"/>
-      <c r="H231" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="232">
-      <c r="A232" s="2" t="inlineStr">
-        <is>
-          <t>ERP.CRE/extensions/Zig365-Commercial-Real-Estate-Property-Management-Contracts-Tests/src/PMBlanketContractLineTest.Codeunit.al</t>
-        </is>
-      </c>
-      <c r="B232" s="2" t="inlineStr">
-        <is>
-          <t>PMBlanketContractLineTest</t>
-        </is>
-      </c>
-      <c r="C232" s="2" t="inlineStr">
-        <is>
-          <t>50101</t>
-        </is>
-      </c>
-      <c r="D232" s="2" t="inlineStr">
-        <is>
-          <t>WhenPropertyOwnerIsEmpty_ExpectError</t>
-        </is>
-      </c>
-      <c r="E232" s="2" t="inlineStr"/>
-      <c r="F232" s="2" t="inlineStr"/>
-      <c r="G232" s="2" t="inlineStr"/>
-      <c r="H232" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="233">
-      <c r="A233" s="2" t="inlineStr">
-        <is>
-          <t>ERP.CRE/extensions/Zig365-Commercial-Real-Estate-Property-Management-Contracts-Tests/src/PropManContractLineTest.Codeunit.al</t>
-        </is>
-      </c>
-      <c r="B233" s="2" t="inlineStr">
-        <is>
-          <t>PropManContractLineTest</t>
-        </is>
-      </c>
-      <c r="C233" s="2" t="inlineStr">
-        <is>
-          <t>50100</t>
-        </is>
-      </c>
-      <c r="D233" s="2" t="inlineStr">
-        <is>
-          <t>WhenInsertFirstLine_LineNoIsCorrectlyDetermined</t>
-        </is>
-      </c>
-      <c r="E233" s="2" t="inlineStr"/>
-      <c r="F233" s="2" t="inlineStr"/>
-      <c r="G233" s="2" t="inlineStr"/>
-      <c r="H233" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="234">
-      <c r="A234" s="2" t="inlineStr">
-        <is>
-          <t>ERP.CRE/extensions/Zig365-Commercial-Real-Estate-Property-Management-Contracts-Tests/src/PropManContractLineTest.Codeunit.al</t>
-        </is>
-      </c>
-      <c r="B234" s="2" t="inlineStr">
-        <is>
-          <t>PropManContractLineTest</t>
-        </is>
-      </c>
-      <c r="C234" s="2" t="inlineStr">
-        <is>
-          <t>50100</t>
-        </is>
-      </c>
-      <c r="D234" s="2" t="inlineStr">
-        <is>
-          <t>WhenInsertSecondLine_LineNoIsCorrectlyDetermined</t>
-        </is>
-      </c>
-      <c r="E234" s="2" t="inlineStr"/>
-      <c r="F234" s="2" t="inlineStr"/>
-      <c r="G234" s="2" t="inlineStr"/>
-      <c r="H234" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="235">
-      <c r="A235" s="2" t="inlineStr">
-        <is>
-          <t>ERP.CRE/extensions/Zig365-Commercial-Real-Estate-Property-Management-Contracts-Tests/src/PropManContractLineTest.Codeunit.al</t>
-        </is>
-      </c>
-      <c r="B235" s="2" t="inlineStr">
-        <is>
-          <t>PropManContractLineTest</t>
-        </is>
-      </c>
-      <c r="C235" s="2" t="inlineStr">
-        <is>
-          <t>50100</t>
-        </is>
-      </c>
-      <c r="D235" s="2" t="inlineStr">
-        <is>
-          <t>WhenStartDateIsEmpty_ExpectError</t>
-        </is>
-      </c>
-      <c r="E235" s="2" t="inlineStr"/>
-      <c r="F235" s="2" t="inlineStr"/>
-      <c r="G235" s="2" t="inlineStr"/>
-      <c r="H235" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="236">
-      <c r="A236" s="2" t="inlineStr">
-        <is>
-          <t>ERP.CRE/extensions/Zig365-Commercial-Real-Estate-Property-Management-Contracts-Tests/src/PropManContractLineTest.Codeunit.al</t>
-        </is>
-      </c>
-      <c r="B236" s="2" t="inlineStr">
-        <is>
-          <t>PropManContractLineTest</t>
-        </is>
-      </c>
-      <c r="C236" s="2" t="inlineStr">
-        <is>
-          <t>50100</t>
-        </is>
-      </c>
-      <c r="D236" s="2" t="inlineStr">
-        <is>
-          <t>WhenValidateStartDateAndNewDateHigherThanContractEndDate_ExpectNewDate</t>
-        </is>
-      </c>
-      <c r="E236" s="2" t="inlineStr"/>
-      <c r="F236" s="2" t="inlineStr"/>
-      <c r="G236" s="2" t="inlineStr"/>
-      <c r="H236" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="237">
-      <c r="A237" s="2" t="inlineStr">
-        <is>
-          <t>ERP.CRE/extensions/Zig365-Commercial-Real-Estate-Property-Management-Contracts-Tests/src/PropManContractLineTest.Codeunit.al</t>
-        </is>
-      </c>
-      <c r="B237" s="2" t="inlineStr">
-        <is>
-          <t>PropManContractLineTest</t>
-        </is>
-      </c>
-      <c r="C237" s="2" t="inlineStr">
-        <is>
-          <t>50100</t>
-        </is>
-      </c>
-      <c r="D237" s="2" t="inlineStr">
-        <is>
-          <t>WhenValidateStartDateAndDateAlreadyExist_ExpectError</t>
-        </is>
-      </c>
-      <c r="E237" s="2" t="inlineStr"/>
-      <c r="F237" s="2" t="inlineStr"/>
-      <c r="G237" s="2" t="inlineStr"/>
-      <c r="H237" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="238">
-      <c r="A238" s="2" t="inlineStr">
-        <is>
-          <t>ERP.CRE/extensions/Zig365-Commercial-Real-Estate-Property-Management-Contracts-Tests/src/PropManContractLineTest.Codeunit.al</t>
-        </is>
-      </c>
-      <c r="B238" s="2" t="inlineStr">
-        <is>
-          <t>PropManContractLineTest</t>
-        </is>
-      </c>
-      <c r="C238" s="2" t="inlineStr">
-        <is>
-          <t>50100</t>
-        </is>
-      </c>
-      <c r="D238" s="2" t="inlineStr">
-        <is>
-          <t>WhenContractLineIsDeletedAndExpensesEntriesExistAfterStartDate_ExpectError</t>
-        </is>
-      </c>
-      <c r="E238" s="2" t="inlineStr"/>
-      <c r="F238" s="2" t="inlineStr"/>
-      <c r="G238" s="2" t="inlineStr"/>
-      <c r="H238" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="239">
-      <c r="A239" s="2" t="inlineStr">
-        <is>
-          <t>ERP.CRE/extensions/Zig365-Commercial-Real-Estate-Property-Management-Contracts-Tests/src/PropManContractLineTest.Codeunit.al</t>
-        </is>
-      </c>
-      <c r="B239" s="2" t="inlineStr">
-        <is>
-          <t>PropManContractLineTest</t>
-        </is>
-      </c>
-      <c r="C239" s="2" t="inlineStr">
-        <is>
-          <t>50100</t>
-        </is>
-      </c>
-      <c r="D239" s="2" t="inlineStr">
-        <is>
-          <t>WhenContractLineIsDeleted_ContractLineElementsAreDeleted</t>
-        </is>
-      </c>
-      <c r="E239" s="2" t="inlineStr"/>
-      <c r="F239" s="2" t="inlineStr"/>
-      <c r="G239" s="2" t="inlineStr"/>
-      <c r="H239" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="240">
-      <c r="A240" s="2" t="inlineStr">
-        <is>
-          <t>ERP.CRE/extensions/Zig365-Commercial-Real-Estate-Property-Management-Contracts-Tests/src/PropManContractLineTest.Codeunit.al</t>
-        </is>
-      </c>
-      <c r="B240" s="2" t="inlineStr">
-        <is>
-          <t>PropManContractLineTest</t>
-        </is>
-      </c>
-      <c r="C240" s="2" t="inlineStr">
-        <is>
-          <t>50100</t>
-        </is>
-      </c>
-      <c r="D240" s="2" t="inlineStr">
-        <is>
-          <t>WhenContractLineIsDeleted_ContractLineLettableObjTypesAreDeleted</t>
-        </is>
-      </c>
-      <c r="E240" s="2" t="inlineStr"/>
-      <c r="F240" s="2" t="inlineStr"/>
-      <c r="G240" s="2" t="inlineStr"/>
-      <c r="H240" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="241">
-      <c r="A241" s="2" t="inlineStr">
-        <is>
-          <t>ERP.CRE/extensions/Zig365-Commercial-Real-Estate-Property-Management-Contracts-Tests/src/PropManContractLineTest.Codeunit.al</t>
-        </is>
-      </c>
-      <c r="B241" s="2" t="inlineStr">
-        <is>
-          <t>PropManContractLineTest</t>
-        </is>
-      </c>
-      <c r="C241" s="2" t="inlineStr">
-        <is>
-          <t>50100</t>
-        </is>
-      </c>
-      <c r="D241" s="2" t="inlineStr">
-        <is>
-          <t>WhenContractLineIsDeleted_ContractLineCostCodesAreDeleted</t>
-        </is>
-      </c>
-      <c r="E241" s="2" t="inlineStr"/>
-      <c r="F241" s="2" t="inlineStr"/>
-      <c r="G241" s="2" t="inlineStr"/>
-      <c r="H241" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="242">
-      <c r="A242" s="2" t="inlineStr">
-        <is>
-          <t>ERP.CRE/extensions/Zig365-Commercial-Real-Estate-Property-Management-Contracts-Tests/src/PropManContractLineTest.Codeunit.al</t>
-        </is>
-      </c>
-      <c r="B242" s="2" t="inlineStr">
-        <is>
-          <t>PropManContractLineTest</t>
-        </is>
-      </c>
-      <c r="C242" s="2" t="inlineStr">
-        <is>
-          <t>50100</t>
-        </is>
-      </c>
-      <c r="D242" s="2" t="inlineStr">
-        <is>
-          <t>WhenContractLineIsDeleted_ContractLineRentBrokeragesAreDeleted</t>
-        </is>
-      </c>
-      <c r="E242" s="2" t="inlineStr"/>
-      <c r="F242" s="2" t="inlineStr"/>
-      <c r="G242" s="2" t="inlineStr"/>
-      <c r="H242" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="243">
-      <c r="A243" s="2" t="inlineStr">
-        <is>
-          <t>ERP.CRE/extensions/Zig365-Commercial-Real-Estate-Property-Management-Contracts-Tests/src/PropManContractLineTest.Codeunit.al</t>
-        </is>
-      </c>
-      <c r="B243" s="2" t="inlineStr">
-        <is>
-          <t>PropManContractLineTest</t>
-        </is>
-      </c>
-      <c r="C243" s="2" t="inlineStr">
-        <is>
-          <t>50100</t>
-        </is>
-      </c>
-      <c r="D243" s="2" t="inlineStr">
-        <is>
-          <t>WhenContractLineIsDeleted_ContractLineFeesAreDeleted</t>
-        </is>
-      </c>
-      <c r="E243" s="2" t="inlineStr"/>
-      <c r="F243" s="2" t="inlineStr"/>
-      <c r="G243" s="2" t="inlineStr"/>
-      <c r="H243" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="244">
-      <c r="A244" s="2" t="inlineStr">
-        <is>
-          <t>ERP.CRE/extensions/Zig365-Commercial-Real-Estate-Property-Management-Contracts-Tests/src/PropManContractLineTest.Codeunit.al</t>
-        </is>
-      </c>
-      <c r="B244" s="2" t="inlineStr">
-        <is>
-          <t>PropManContractLineTest</t>
-        </is>
-      </c>
-      <c r="C244" s="2" t="inlineStr">
-        <is>
-          <t>50100</t>
-        </is>
-      </c>
-      <c r="D244" s="2" t="inlineStr">
-        <is>
-          <t>WhenLettableObjectTypeIsEmpty_ExpectError</t>
-        </is>
-      </c>
-      <c r="E244" s="2" t="inlineStr"/>
-      <c r="F244" s="2" t="inlineStr"/>
-      <c r="G244" s="2" t="inlineStr"/>
-      <c r="H244" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="245">
-      <c r="A245" s="2" t="inlineStr">
-        <is>
-          <t>ERP.CRE/extensions/Zig365-Commercial-Real-Estate-Property-Management-Contracts-Tests/src/PropManContractLineTest.Codeunit.al</t>
-        </is>
-      </c>
-      <c r="B245" s="2" t="inlineStr">
-        <is>
-          <t>PropManContractLineTest</t>
-        </is>
-      </c>
-      <c r="C245" s="2" t="inlineStr">
-        <is>
-          <t>50100</t>
-        </is>
-      </c>
-      <c r="D245" s="2" t="inlineStr">
-        <is>
-          <t>WhenInsertLineAndContractHasNoPropertyOwner_ExpectError</t>
-        </is>
-      </c>
-      <c r="E245" s="2" t="inlineStr"/>
-      <c r="F245" s="2" t="inlineStr"/>
-      <c r="G245" s="2" t="inlineStr"/>
-      <c r="H245" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="246">
-      <c r="A246" s="2" t="inlineStr">
-        <is>
-          <t>ERP.CRE/extensions/Zig365-Commercial-Real-Estate-Property-Management-Contracts-Tests/src/PropManContractLineTest.Codeunit.al</t>
-        </is>
-      </c>
-      <c r="B246" s="2" t="inlineStr">
-        <is>
-          <t>PropManContractLineTest</t>
-        </is>
-      </c>
-      <c r="C246" s="2" t="inlineStr">
-        <is>
-          <t>50100</t>
-        </is>
-      </c>
-      <c r="D246" s="2" t="inlineStr">
-        <is>
-          <t>WhenValidateStartDateAndContractHasEmptyStartDate_ExpectError</t>
-        </is>
-      </c>
-      <c r="E246" s="2" t="inlineStr"/>
-      <c r="F246" s="2" t="inlineStr"/>
-      <c r="G246" s="2" t="inlineStr"/>
-      <c r="H246" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="247">
-      <c r="A247" s="2" t="inlineStr">
-        <is>
-          <t>ERP.CRE/extensions/Zig365-Commercial-Real-Estate-Property-Management-Contracts-Tests/src/PropManContractLineTest.Codeunit.al</t>
-        </is>
-      </c>
-      <c r="B247" s="2" t="inlineStr">
-        <is>
-          <t>PropManContractLineTest</t>
-        </is>
-      </c>
-      <c r="C247" s="2" t="inlineStr">
-        <is>
-          <t>50100</t>
-        </is>
-      </c>
-      <c r="D247" s="2" t="inlineStr">
-        <is>
-          <t>WhenSetStartDateToADateBeforeContractStartDate_ExpectError</t>
-        </is>
-      </c>
-      <c r="E247" s="2" t="inlineStr"/>
-      <c r="F247" s="2" t="inlineStr"/>
-      <c r="G247" s="2" t="inlineStr"/>
-      <c r="H247" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="248">
-      <c r="A248" s="2" t="inlineStr">
-        <is>
-          <t>ERP.CRE/extensions/Zig365-Commercial-Real-Estate-Property-Management-Contracts-Tests/src/BlankCtrLineRentBrokerageTest.Codeunit.al</t>
-        </is>
-      </c>
-      <c r="B248" s="2" t="inlineStr">
-        <is>
-          <t>BlankCtrLineRentBrokerageTest</t>
-        </is>
-      </c>
-      <c r="C248" s="2" t="inlineStr">
-        <is>
-          <t>50109</t>
-        </is>
-      </c>
-      <c r="D248" s="2" t="inlineStr">
-        <is>
-          <t>WhenAmountBasedOnIsChangedFromFixedAmountToBaseRent_ExpectAmountToBeZero</t>
-        </is>
-      </c>
-      <c r="E248" s="2" t="inlineStr"/>
-      <c r="F248" s="2" t="inlineStr"/>
-      <c r="G248" s="2" t="inlineStr"/>
-      <c r="H248" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="249">
-      <c r="A249" s="2" t="inlineStr">
-        <is>
-          <t>ERP.CRE/extensions/Zig365-Commercial-Real-Estate-Property-Management-Contracts-Tests/src/BlankCtrLineRentBrokerageTest.Codeunit.al</t>
-        </is>
-      </c>
-      <c r="B249" s="2" t="inlineStr">
-        <is>
-          <t>BlankCtrLineRentBrokerageTest</t>
-        </is>
-      </c>
-      <c r="C249" s="2" t="inlineStr">
-        <is>
-          <t>50109</t>
-        </is>
-      </c>
-      <c r="D249" s="2" t="inlineStr">
-        <is>
-          <t>WhenAmountBasedOnIsChangedFromBaseRentToFixedAmount_ExpectPercentageToBeZero</t>
-        </is>
-      </c>
-      <c r="E249" s="2" t="inlineStr"/>
-      <c r="F249" s="2" t="inlineStr"/>
-      <c r="G249" s="2" t="inlineStr"/>
-      <c r="H249" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="250">
-      <c r="A250" s="2" t="inlineStr">
-        <is>
-          <t>ERP.CRE/extensions/Zig365-Commercial-Real-Estate-Property-Management-Contracts-Tests/src/PropertyOwnerHistoryTest.Codeunit.al</t>
-        </is>
-      </c>
-      <c r="B250" s="2" t="inlineStr">
-        <is>
-          <t>PropertyOwnerHistoryTest</t>
-        </is>
-      </c>
-      <c r="C250" s="2" t="inlineStr">
-        <is>
-          <t>50118</t>
-        </is>
-      </c>
-      <c r="D250" s="2" t="inlineStr">
-        <is>
-          <t>WhenGetPropertyOwnerHistory_ExpectCorrectValues</t>
-        </is>
-      </c>
-      <c r="E250" s="2" t="inlineStr"/>
-      <c r="F250" s="2" t="inlineStr"/>
-      <c r="G250" s="2" t="inlineStr"/>
-      <c r="H250" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="251">
-      <c r="A251" s="2" t="inlineStr">
-        <is>
-          <t>ERP.CRE/extensions/Zig365-Commercial-Real-Estate-Property-Management-Contracts-Tests/src/PropertyOwnerHistoryTest.Codeunit.al</t>
-        </is>
-      </c>
-      <c r="B251" s="2" t="inlineStr">
-        <is>
-          <t>PropertyOwnerHistoryTest</t>
-        </is>
-      </c>
-      <c r="C251" s="2" t="inlineStr">
-        <is>
-          <t>50118</t>
-        </is>
-      </c>
-      <c r="D251" s="2" t="inlineStr">
-        <is>
-          <t>WhenGetPropertyOwnerHistoryAndNoCContract_ExpectEmptyResult</t>
-        </is>
-      </c>
-      <c r="E251" s="2" t="inlineStr"/>
-      <c r="F251" s="2" t="inlineStr"/>
-      <c r="G251" s="2" t="inlineStr"/>
-      <c r="H251" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="252">
-      <c r="A252" s="2" t="inlineStr">
-        <is>
-          <t>ERP.CRE/extensions/Zig365-Commercial-Real-Estate-Property-Management-Contracts-Tests/src/SalesDocumentOwnerStmTest.Codeunit.al</t>
-        </is>
-      </c>
-      <c r="B252" s="2" t="inlineStr">
-        <is>
-          <t>SalesDocumentOwnerStmTest</t>
-        </is>
-      </c>
-      <c r="C252" s="2" t="inlineStr">
-        <is>
-          <t>50123</t>
-        </is>
-      </c>
-      <c r="D252" s="2" t="inlineStr">
-        <is>
-          <t>WhenModifyingSalesLineForCreditMemoOwnerStatement_ExpectError</t>
-        </is>
-      </c>
-      <c r="E252" s="2" t="inlineStr"/>
-      <c r="F252" s="2" t="inlineStr"/>
-      <c r="G252" s="2" t="inlineStr"/>
-      <c r="H252" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="253">
-      <c r="A253" s="2" t="inlineStr">
-        <is>
-          <t>ERP.CRE/extensions/Zig365-Commercial-Real-Estate-Property-Management-Contracts-Tests/src/SalesDocumentOwnerStmTest.Codeunit.al</t>
-        </is>
-      </c>
-      <c r="B253" s="2" t="inlineStr">
-        <is>
-          <t>SalesDocumentOwnerStmTest</t>
-        </is>
-      </c>
-      <c r="C253" s="2" t="inlineStr">
-        <is>
-          <t>50123</t>
-        </is>
-      </c>
-      <c r="D253" s="2" t="inlineStr">
-        <is>
-          <t>WhenDeletingSalesLineForCreditMemoOwnerStatement_ExpectError</t>
-        </is>
-      </c>
-      <c r="E253" s="2" t="inlineStr"/>
-      <c r="F253" s="2" t="inlineStr"/>
-      <c r="G253" s="2" t="inlineStr"/>
-      <c r="H253" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="254">
-      <c r="A254" s="2" t="inlineStr">
-        <is>
-          <t>ERP.CRE/extensions/Zig365-Commercial-Real-Estate-Property-Management-Contracts-Tests/src/SalesDocumentOwnerStmTest.Codeunit.al</t>
-        </is>
-      </c>
-      <c r="B254" s="2" t="inlineStr">
-        <is>
-          <t>SalesDocumentOwnerStmTest</t>
-        </is>
-      </c>
-      <c r="C254" s="2" t="inlineStr">
-        <is>
-          <t>50123</t>
-        </is>
-      </c>
-      <c r="D254" s="2" t="inlineStr">
-        <is>
-          <t>WhenDeletingSalesCreditMemoOfTypeOwnerStatement_ExpectPostedCheckIsReset</t>
-        </is>
-      </c>
-      <c r="E254" s="2" t="inlineStr"/>
-      <c r="F254" s="2" t="inlineStr"/>
-      <c r="G254" s="2" t="inlineStr"/>
-      <c r="H254" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="255">
-      <c r="A255" s="2" t="inlineStr">
-        <is>
-          <t>ERP.CRE/extensions/Zig365-Commercial-Real-Estate-Property-Management-Contracts-Tests/src/SalesDocumentOwnerStmTest.Codeunit.al</t>
-        </is>
-      </c>
-      <c r="B255" s="2" t="inlineStr">
-        <is>
-          <t>SalesDocumentOwnerStmTest</t>
-        </is>
-      </c>
-      <c r="C255" s="2" t="inlineStr">
-        <is>
-          <t>50123</t>
-        </is>
-      </c>
-      <c r="D255" s="2" t="inlineStr">
-        <is>
-          <t>WhenCopyingSalesInvoice_ExpectOwnerStatementFieldsAreReset</t>
-        </is>
-      </c>
-      <c r="E255" s="2" t="inlineStr"/>
-      <c r="F255" s="2" t="inlineStr"/>
-      <c r="G255" s="2" t="inlineStr"/>
-      <c r="H255" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="256">
-      <c r="A256" s="2" t="inlineStr">
-        <is>
-          <t>ERP.CRE/extensions/Zig365-Commercial-Real-Estate-Property-Management-Contracts-Tests/src/SalesDocumentOwnerStmTest.Codeunit.al</t>
-        </is>
-      </c>
-      <c r="B256" s="2" t="inlineStr">
-        <is>
-          <t>SalesDocumentOwnerStmTest</t>
-        </is>
-      </c>
-      <c r="C256" s="2" t="inlineStr">
-        <is>
-          <t>50123</t>
-        </is>
-      </c>
-      <c r="D256" s="2" t="inlineStr">
-        <is>
-          <t>WhenCreatingSalesLineWithDimensionPriorities_ExpectDimensionTakenFromGLAccount</t>
-        </is>
-      </c>
-      <c r="E256" s="2" t="inlineStr"/>
-      <c r="F256" s="2" t="inlineStr"/>
-      <c r="G256" s="2" t="inlineStr"/>
-      <c r="H256" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="257">
-      <c r="A257" s="2" t="inlineStr">
-        <is>
-          <t>ERP.CRE/extensions/Zig365-Commercial-Real-Estate-Property-Management-Contracts-Tests/src/SalesDocumentOwnerStmTest.Codeunit.al</t>
-        </is>
-      </c>
-      <c r="B257" s="2" t="inlineStr">
-        <is>
-          <t>SalesDocumentOwnerStmTest</t>
-        </is>
-      </c>
-      <c r="C257" s="2" t="inlineStr">
-        <is>
-          <t>50123</t>
-        </is>
-      </c>
-      <c r="D257" s="2" t="inlineStr">
-        <is>
-          <t>WhenCreatingSalesLineWithDimensionPriorities_ExpectDimensionTakenFromCluster</t>
-        </is>
-      </c>
-      <c r="E257" s="2" t="inlineStr"/>
-      <c r="F257" s="2" t="inlineStr"/>
-      <c r="G257" s="2" t="inlineStr"/>
-      <c r="H257" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="258">
-      <c r="A258" s="2" t="inlineStr">
-        <is>
-          <t>ERP.CRE/extensions/Zig365-Commercial-Real-Estate-Property-Management-Contracts-Tests/src/SalesDocumentOwnerStmTest.Codeunit.al</t>
-        </is>
-      </c>
-      <c r="B258" s="2" t="inlineStr">
-        <is>
-          <t>SalesDocumentOwnerStmTest</t>
-        </is>
-      </c>
-      <c r="C258" s="2" t="inlineStr">
-        <is>
-          <t>50123</t>
-        </is>
-      </c>
-      <c r="D258" s="2" t="inlineStr">
-        <is>
-          <t>WhenPostingSalesInvoiceWithOwnerStatement_SourceCodeAndSettledUntilAreCorrect</t>
-        </is>
-      </c>
-      <c r="E258" s="2" t="inlineStr"/>
-      <c r="F258" s="2" t="inlineStr"/>
-      <c r="G258" s="2" t="inlineStr"/>
-      <c r="H258" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="259">
-      <c r="A259" s="2" t="inlineStr">
-        <is>
-          <t>ERP.CRE/extensions/Zig365-Commercial-Real-Estate-Property-Management-Contracts-Tests/src/SalesDocumentOwnerStmTest.Codeunit.al</t>
-        </is>
-      </c>
-      <c r="B259" s="2" t="inlineStr">
-        <is>
-          <t>SalesDocumentOwnerStmTest</t>
-        </is>
-      </c>
-      <c r="C259" s="2" t="inlineStr">
-        <is>
-          <t>50123</t>
-        </is>
-      </c>
-      <c r="D259" s="2" t="inlineStr">
-        <is>
-          <t>WhenPostingSalesInvoiceWithOwnerStatementCostsAndFullVAT_FullVATIsPostedOnPurchaseAccount</t>
-        </is>
-      </c>
-      <c r="E259" s="2" t="inlineStr"/>
-      <c r="F259" s="2" t="inlineStr"/>
-      <c r="G259" s="2" t="inlineStr"/>
-      <c r="H259" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="260">
-      <c r="A260" s="2" t="inlineStr">
-        <is>
-          <t>ERP.CRE/extensions/Zig365-Commercial-Real-Estate-Property-Management-Contracts-Tests/src/AlternateCostCodeTest.Codeunit.al</t>
-        </is>
-      </c>
-      <c r="B260" s="2" t="inlineStr">
-        <is>
-          <t>AlternateCostCodeTest</t>
-        </is>
-      </c>
-      <c r="C260" s="2" t="inlineStr">
-        <is>
-          <t>50113</t>
-        </is>
-      </c>
-      <c r="D260" s="2" t="inlineStr">
-        <is>
-          <t>WhenNoContractLineCostCodeIsDefinedForPropertyOwner_ExpectError</t>
-        </is>
-      </c>
-      <c r="E260" s="2" t="inlineStr"/>
-      <c r="F260" s="2" t="inlineStr"/>
-      <c r="G260" s="2" t="inlineStr"/>
-      <c r="H260" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="261">
-      <c r="A261" s="2" t="inlineStr">
-        <is>
-          <t>ERP.CRE/extensions/Zig365-Commercial-Real-Estate-Property-Management-Contracts-Tests/src/AlternateCostCodeTest.Codeunit.al</t>
-        </is>
-      </c>
-      <c r="B261" s="2" t="inlineStr">
-        <is>
-          <t>AlternateCostCodeTest</t>
-        </is>
-      </c>
-      <c r="C261" s="2" t="inlineStr">
-        <is>
-          <t>50113</t>
-        </is>
-      </c>
-      <c r="D261" s="2" t="inlineStr">
-        <is>
-          <t>AllUniqueContractLineCostCodesAreCollectedPerPropertyOwner</t>
-        </is>
-      </c>
-      <c r="E261" s="2" t="inlineStr"/>
-      <c r="F261" s="2" t="inlineStr"/>
-      <c r="G261" s="2" t="inlineStr"/>
-      <c r="H261" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="262">
-      <c r="A262" s="2" t="inlineStr">
-        <is>
-          <t>ERP.CRE/extensions/Zig365-Commercial-Real-Estate-Property-Management-Contracts-Tests/src/ExpensesEntryTest.Codeunit.al</t>
-        </is>
-      </c>
-      <c r="B262" s="2" t="inlineStr">
-        <is>
-          <t>ExpensesEntryTest</t>
-        </is>
-      </c>
-      <c r="C262" s="2" t="inlineStr">
-        <is>
-          <t>50114</t>
-        </is>
-      </c>
-      <c r="D262" s="2" t="inlineStr">
-        <is>
-          <t>GenJnlLineWithCostCode_BlanketContractLineActiveWithCostCode_ExpectExpensesEntryIsUpdated</t>
-        </is>
-      </c>
-      <c r="E262" s="2" t="inlineStr"/>
-      <c r="F262" s="2" t="inlineStr"/>
-      <c r="G262" s="2" t="inlineStr"/>
-      <c r="H262" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="263">
-      <c r="A263" s="2" t="inlineStr">
-        <is>
-          <t>ERP.CRE/extensions/Zig365-Commercial-Real-Estate-Property-Management-Contracts-Tests/src/ExpensesEntryTest.Codeunit.al</t>
-        </is>
-      </c>
-      <c r="B263" s="2" t="inlineStr">
-        <is>
-          <t>ExpensesEntryTest</t>
-        </is>
-      </c>
-      <c r="C263" s="2" t="inlineStr">
-        <is>
-          <t>50114</t>
-        </is>
-      </c>
-      <c r="D263" s="2" t="inlineStr">
-        <is>
-          <t>GenJnlLineWithCostCode_WhenBlanketContractLineCostCodeNotExists_ExpectError</t>
-        </is>
-      </c>
-      <c r="E263" s="2" t="inlineStr"/>
-      <c r="F263" s="2" t="inlineStr"/>
-      <c r="G263" s="2" t="inlineStr"/>
-      <c r="H263" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="264">
-      <c r="A264" s="2" t="inlineStr">
-        <is>
-          <t>ERP.CRE/extensions/Zig365-Commercial-Real-Estate-Property-Management-Contracts-Tests/src/ExpensesEntryTest.Codeunit.al</t>
-        </is>
-      </c>
-      <c r="B264" s="2" t="inlineStr">
-        <is>
-          <t>ExpensesEntryTest</t>
-        </is>
-      </c>
-      <c r="C264" s="2" t="inlineStr">
-        <is>
-          <t>50114</t>
-        </is>
-      </c>
-      <c r="D264" s="2" t="inlineStr">
-        <is>
-          <t>GenJnlLineWithCostCode_WhenContractLineActiveWithCostCode_ExpectExpensesEntryIsUpdated</t>
-        </is>
-      </c>
-      <c r="E264" s="2" t="inlineStr"/>
-      <c r="F264" s="2" t="inlineStr"/>
-      <c r="G264" s="2" t="inlineStr"/>
-      <c r="H264" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="265">
-      <c r="A265" s="2" t="inlineStr">
-        <is>
-          <t>ERP.CRE/extensions/Zig365-Commercial-Real-Estate-Property-Management-Contracts-Tests/src/ExpensesEntryTest.Codeunit.al</t>
-        </is>
-      </c>
-      <c r="B265" s="2" t="inlineStr">
-        <is>
-          <t>ExpensesEntryTest</t>
-        </is>
-      </c>
-      <c r="C265" s="2" t="inlineStr">
-        <is>
-          <t>50114</t>
-        </is>
-      </c>
-      <c r="D265" s="2" t="inlineStr">
-        <is>
-          <t>GenJnlLineWithCostCodeAndOwnerStatementCluster_WhenContractLineActiveWithCostCode_ExpectExpensesEntryIsUpdated</t>
-        </is>
-      </c>
-      <c r="E265" s="2" t="inlineStr"/>
-      <c r="F265" s="2" t="inlineStr"/>
-      <c r="G265" s="2" t="inlineStr"/>
-      <c r="H265" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="266">
-      <c r="A266" s="2" t="inlineStr">
-        <is>
-          <t>ERP.CRE/extensions/Zig365-Commercial-Real-Estate-Property-Management-Contracts-Tests/src/ExpensesEntryTest.Codeunit.al</t>
-        </is>
-      </c>
-      <c r="B266" s="2" t="inlineStr">
-        <is>
-          <t>ExpensesEntryTest</t>
-        </is>
-      </c>
-      <c r="C266" s="2" t="inlineStr">
-        <is>
-          <t>50114</t>
-        </is>
-      </c>
-      <c r="D266" s="2" t="inlineStr">
-        <is>
-          <t>GenJnlLineWithCostCodeAndTechnicalCluster_ExpectNoExpensesEntryCreated</t>
-        </is>
-      </c>
-      <c r="E266" s="2" t="inlineStr"/>
-      <c r="F266" s="2" t="inlineStr"/>
-      <c r="G266" s="2" t="inlineStr"/>
-      <c r="H266" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="267">
-      <c r="A267" s="2" t="inlineStr">
-        <is>
-          <t>ERP.CRE/extensions/Zig365-Commercial-Real-Estate-Property-Management-Contracts-Tests/src/ExpensesEntryTest.Codeunit.al</t>
-        </is>
-      </c>
-      <c r="B267" s="2" t="inlineStr">
-        <is>
-          <t>ExpensesEntryTest</t>
-        </is>
-      </c>
-      <c r="C267" s="2" t="inlineStr">
-        <is>
-          <t>50114</t>
-        </is>
-      </c>
-      <c r="D267" s="2" t="inlineStr">
-        <is>
-          <t>GenJnlLineWithCostCode_WhenNoContractActive_ExpectError</t>
-        </is>
-      </c>
-      <c r="E267" s="2" t="inlineStr"/>
-      <c r="F267" s="2" t="inlineStr"/>
-      <c r="G267" s="2" t="inlineStr"/>
-      <c r="H267" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="268">
-      <c r="A268" s="2" t="inlineStr">
-        <is>
-          <t>ERP.CRE/extensions/Zig365-Commercial-Real-Estate-Property-Management-Contracts-Tests/src/ExpensesEntryTest.Codeunit.al</t>
-        </is>
-      </c>
-      <c r="B268" s="2" t="inlineStr">
-        <is>
-          <t>ExpensesEntryTest</t>
-        </is>
-      </c>
-      <c r="C268" s="2" t="inlineStr">
-        <is>
-          <t>50114</t>
-        </is>
-      </c>
-      <c r="D268" s="2" t="inlineStr">
-        <is>
-          <t>GenJnlLineWithCostCodeAndOwnerStatementCluster_WhenNoContractActive_ExpectError</t>
-        </is>
-      </c>
-      <c r="E268" s="2" t="inlineStr"/>
-      <c r="F268" s="2" t="inlineStr"/>
-      <c r="G268" s="2" t="inlineStr"/>
-      <c r="H268" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="269">
-      <c r="A269" s="2" t="inlineStr">
-        <is>
-          <t>ERP.CRE/extensions/Zig365-Commercial-Real-Estate-Property-Management-Contracts-Tests/src/ExpensesEntryTest.Codeunit.al</t>
-        </is>
-      </c>
-      <c r="B269" s="2" t="inlineStr">
-        <is>
-          <t>ExpensesEntryTest</t>
-        </is>
-      </c>
-      <c r="C269" s="2" t="inlineStr">
-        <is>
-          <t>50114</t>
-        </is>
-      </c>
-      <c r="D269" s="2" t="inlineStr">
-        <is>
-          <t>GenJnlLineWithCostCode_WhenNoContractLineActive_ExpectError</t>
-        </is>
-      </c>
-      <c r="E269" s="2" t="inlineStr"/>
-      <c r="F269" s="2" t="inlineStr"/>
-      <c r="G269" s="2" t="inlineStr"/>
-      <c r="H269" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="270">
-      <c r="A270" s="2" t="inlineStr">
-        <is>
-          <t>ERP.CRE/extensions/Zig365-Commercial-Real-Estate-Property-Management-Contracts-Tests/src/ExpensesEntryTest.Codeunit.al</t>
-        </is>
-      </c>
-      <c r="B270" s="2" t="inlineStr">
-        <is>
-          <t>ExpensesEntryTest</t>
-        </is>
-      </c>
-      <c r="C270" s="2" t="inlineStr">
-        <is>
-          <t>50114</t>
-        </is>
-      </c>
-      <c r="D270" s="2" t="inlineStr">
-        <is>
-          <t>WhenBlanketContractLineActiveWithCostCode_ExpectExpensesEntryIsUpdated</t>
-        </is>
-      </c>
-      <c r="E270" s="2" t="inlineStr"/>
-      <c r="F270" s="2" t="inlineStr"/>
-      <c r="G270" s="2" t="inlineStr"/>
-      <c r="H270" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="271">
-      <c r="A271" s="2" t="inlineStr">
-        <is>
-          <t>ERP.CRE/extensions/Zig365-Commercial-Real-Estate-Property-Management-Contracts-Tests/src/ExpensesEntryTest.Codeunit.al</t>
-        </is>
-      </c>
-      <c r="B271" s="2" t="inlineStr">
-        <is>
-          <t>ExpensesEntryTest</t>
-        </is>
-      </c>
-      <c r="C271" s="2" t="inlineStr">
-        <is>
-          <t>50114</t>
-        </is>
-      </c>
-      <c r="D271" s="2" t="inlineStr">
-        <is>
-          <t>WhenBlanketContractLineActiveWithCostCodeAndOwnerStatementCluster_ExpectExpensesEntryIsUpdated</t>
-        </is>
-      </c>
-      <c r="E271" s="2" t="inlineStr"/>
-      <c r="F271" s="2" t="inlineStr"/>
-      <c r="G271" s="2" t="inlineStr"/>
-      <c r="H271" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="272">
-      <c r="A272" s="2" t="inlineStr">
-        <is>
-          <t>ERP.CRE/extensions/Zig365-Commercial-Real-Estate-Property-Management-Contracts-Tests/src/ExpensesEntryTest.Codeunit.al</t>
-        </is>
-      </c>
-      <c r="B272" s="2" t="inlineStr">
-        <is>
-          <t>ExpensesEntryTest</t>
-        </is>
-      </c>
-      <c r="C272" s="2" t="inlineStr">
-        <is>
-          <t>50114</t>
-        </is>
-      </c>
-      <c r="D272" s="2" t="inlineStr">
-        <is>
-          <t>WhenBlanketContractLineCostCodeNotExists_ExpectError</t>
-        </is>
-      </c>
-      <c r="E272" s="2" t="inlineStr"/>
-      <c r="F272" s="2" t="inlineStr"/>
-      <c r="G272" s="2" t="inlineStr"/>
-      <c r="H272" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="273">
-      <c r="A273" s="2" t="inlineStr">
-        <is>
-          <t>ERP.CRE/extensions/Zig365-Commercial-Real-Estate-Property-Management-Contracts-Tests/src/ExpensesEntryTest.Codeunit.al</t>
-        </is>
-      </c>
-      <c r="B273" s="2" t="inlineStr">
-        <is>
-          <t>ExpensesEntryTest</t>
-        </is>
-      </c>
-      <c r="C273" s="2" t="inlineStr">
-        <is>
-          <t>50114</t>
-        </is>
-      </c>
-      <c r="D273" s="2" t="inlineStr">
-        <is>
-          <t>WhenContractLineActiveWithCostCode_ExpectExpensesEntryIsUpdated</t>
-        </is>
-      </c>
-      <c r="E273" s="2" t="inlineStr"/>
-      <c r="F273" s="2" t="inlineStr"/>
-      <c r="G273" s="2" t="inlineStr"/>
-      <c r="H273" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="274">
-      <c r="A274" s="2" t="inlineStr">
-        <is>
-          <t>ERP.CRE/extensions/Zig365-Commercial-Real-Estate-Property-Management-Contracts-Tests/src/ExpensesEntryTest.Codeunit.al</t>
-        </is>
-      </c>
-      <c r="B274" s="2" t="inlineStr">
-        <is>
-          <t>ExpensesEntryTest</t>
-        </is>
-      </c>
-      <c r="C274" s="2" t="inlineStr">
-        <is>
-          <t>50114</t>
-        </is>
-      </c>
-      <c r="D274" s="2" t="inlineStr">
-        <is>
-          <t>WhenTechnicalCluster_ExpectNoExpensesEntryCreated</t>
-        </is>
-      </c>
-      <c r="E274" s="2" t="inlineStr"/>
-      <c r="F274" s="2" t="inlineStr"/>
-      <c r="G274" s="2" t="inlineStr"/>
-      <c r="H274" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="275">
-      <c r="A275" s="2" t="inlineStr">
-        <is>
-          <t>ERP.CRE/extensions/Zig365-Commercial-Real-Estate-Property-Management-Contracts-Tests/src/ExpensesEntryTest.Codeunit.al</t>
-        </is>
-      </c>
-      <c r="B275" s="2" t="inlineStr">
-        <is>
-          <t>ExpensesEntryTest</t>
-        </is>
-      </c>
-      <c r="C275" s="2" t="inlineStr">
-        <is>
-          <t>50114</t>
-        </is>
-      </c>
-      <c r="D275" s="2" t="inlineStr">
-        <is>
-          <t>WhenContractLineCostCodeNotExists_ExpectError</t>
-        </is>
-      </c>
-      <c r="E275" s="2" t="inlineStr"/>
-      <c r="F275" s="2" t="inlineStr"/>
-      <c r="G275" s="2" t="inlineStr"/>
-      <c r="H275" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="276">
-      <c r="A276" s="2" t="inlineStr">
-        <is>
-          <t>ERP.CRE/extensions/Zig365-Commercial-Real-Estate-Property-Management-Contracts-Tests/src/ExpensesEntryTest.Codeunit.al</t>
-        </is>
-      </c>
-      <c r="B276" s="2" t="inlineStr">
-        <is>
-          <t>ExpensesEntryTest</t>
-        </is>
-      </c>
-      <c r="C276" s="2" t="inlineStr">
-        <is>
-          <t>50114</t>
-        </is>
-      </c>
-      <c r="D276" s="2" t="inlineStr">
-        <is>
-          <t>WhenNoBlanketContractLineActive_ExpectError</t>
-        </is>
-      </c>
-      <c r="E276" s="2" t="inlineStr"/>
-      <c r="F276" s="2" t="inlineStr"/>
-      <c r="G276" s="2" t="inlineStr"/>
-      <c r="H276" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="277">
-      <c r="A277" s="2" t="inlineStr">
-        <is>
-          <t>ERP.CRE/extensions/Zig365-Commercial-Real-Estate-Property-Management-Contracts-Tests/src/ExpensesEntryTest.Codeunit.al</t>
-        </is>
-      </c>
-      <c r="B277" s="2" t="inlineStr">
-        <is>
-          <t>ExpensesEntryTest</t>
-        </is>
-      </c>
-      <c r="C277" s="2" t="inlineStr">
-        <is>
-          <t>50114</t>
-        </is>
-      </c>
-      <c r="D277" s="2" t="inlineStr">
-        <is>
-          <t>WhenNoContractActive_ExpectError</t>
-        </is>
-      </c>
-      <c r="E277" s="2" t="inlineStr"/>
-      <c r="F277" s="2" t="inlineStr"/>
-      <c r="G277" s="2" t="inlineStr"/>
-      <c r="H277" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="278">
-      <c r="A278" s="2" t="inlineStr">
-        <is>
-          <t>ERP.CRE/extensions/Zig365-Commercial-Real-Estate-Property-Management-Contracts-Tests/src/ExpensesEntryTest.Codeunit.al</t>
-        </is>
-      </c>
-      <c r="B278" s="2" t="inlineStr">
-        <is>
-          <t>ExpensesEntryTest</t>
-        </is>
-      </c>
-      <c r="C278" s="2" t="inlineStr">
-        <is>
-          <t>50114</t>
-        </is>
-      </c>
-      <c r="D278" s="2" t="inlineStr">
-        <is>
-          <t>WhenNoContractActiveAndOwnerStatementCluster_ExpectError</t>
-        </is>
-      </c>
-      <c r="E278" s="2" t="inlineStr"/>
-      <c r="F278" s="2" t="inlineStr"/>
-      <c r="G278" s="2" t="inlineStr"/>
-      <c r="H278" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="279">
-      <c r="A279" s="2" t="inlineStr">
-        <is>
-          <t>ERP.CRE/extensions/Zig365-Commercial-Real-Estate-Property-Management-Contracts-Tests/src/ExpensesEntryTest.Codeunit.al</t>
-        </is>
-      </c>
-      <c r="B279" s="2" t="inlineStr">
-        <is>
-          <t>ExpensesEntryTest</t>
-        </is>
-      </c>
-      <c r="C279" s="2" t="inlineStr">
-        <is>
-          <t>50114</t>
-        </is>
-      </c>
-      <c r="D279" s="2" t="inlineStr">
-        <is>
-          <t>WhenNoContractLineActive_ExpectError</t>
-        </is>
-      </c>
-      <c r="E279" s="2" t="inlineStr"/>
-      <c r="F279" s="2" t="inlineStr"/>
-      <c r="G279" s="2" t="inlineStr"/>
-      <c r="H279" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="280">
-      <c r="A280" s="2" t="inlineStr">
-        <is>
-          <t>ERP.CRE/extensions/Zig365-Commercial-Real-Estate-Property-Management-Contracts-Tests/src/ContractLineCostCodeTest.Codeunit.al</t>
-        </is>
-      </c>
-      <c r="B280" s="2" t="inlineStr">
-        <is>
-          <t>ContractLineCostCodeTest</t>
-        </is>
-      </c>
-      <c r="C280" s="2" t="inlineStr">
-        <is>
-          <t>50126</t>
-        </is>
-      </c>
-      <c r="D280" s="2" t="inlineStr">
-        <is>
-          <t>WhenAddSelectedCostCodes_CostCodesAreAddedToPropManContract</t>
-        </is>
-      </c>
-      <c r="E280" s="2" t="inlineStr"/>
-      <c r="F280" s="2" t="inlineStr"/>
-      <c r="G280" s="2" t="inlineStr"/>
-      <c r="H280" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="281">
-      <c r="A281" s="2" t="inlineStr">
-        <is>
-          <t>ERP.CRE/extensions/Zig365-Commercial-Real-Estate-Property-Management-Contracts-Tests/src/ContractLineCostCodeTest.Codeunit.al</t>
-        </is>
-      </c>
-      <c r="B281" s="2" t="inlineStr">
-        <is>
-          <t>ContractLineCostCodeTest</t>
-        </is>
-      </c>
-      <c r="C281" s="2" t="inlineStr">
-        <is>
-          <t>50126</t>
-        </is>
-      </c>
-      <c r="D281" s="2" t="inlineStr">
-        <is>
-          <t>WhenAddSelectedCostCodes_CostCodesAreAddedToPMBlanketContract</t>
-        </is>
-      </c>
-      <c r="E281" s="2" t="inlineStr"/>
-      <c r="F281" s="2" t="inlineStr"/>
-      <c r="G281" s="2" t="inlineStr"/>
-      <c r="H281" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="282">
-      <c r="A282" s="2" t="inlineStr">
-        <is>
-          <t>ERP.CRE/extensions/Zig365-Commercial-Real-Estate-Property-Management-Contracts-Tests/src/CreateOwnerStatementErrorMsgs.Codeunit.al</t>
-        </is>
-      </c>
-      <c r="B282" s="2" t="inlineStr">
-        <is>
-          <t>CreateOwnerStatementErrorMsgs</t>
-        </is>
-      </c>
-      <c r="C282" s="2" t="inlineStr">
-        <is>
-          <t>50119</t>
-        </is>
-      </c>
-      <c r="D282" s="2" t="inlineStr">
-        <is>
-          <t>CheckPeriodToSettle_FutureMonthSelected</t>
-        </is>
-      </c>
-      <c r="E282" s="2" t="inlineStr"/>
-      <c r="F282" s="2" t="inlineStr"/>
-      <c r="G282" s="2" t="inlineStr"/>
-      <c r="H282" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="283">
-      <c r="A283" s="2" t="inlineStr">
-        <is>
-          <t>ERP.CRE/extensions/Zig365-Commercial-Real-Estate-Property-Management-Contracts-Tests/src/CreateOwnerStatementErrorMsgs.Codeunit.al</t>
-        </is>
-      </c>
-      <c r="B283" s="2" t="inlineStr">
-        <is>
-          <t>CreateOwnerStatementErrorMsgs</t>
-        </is>
-      </c>
-      <c r="C283" s="2" t="inlineStr">
-        <is>
-          <t>50119</t>
-        </is>
-      </c>
-      <c r="D283" s="2" t="inlineStr">
-        <is>
-          <t>CheckPeriodToSettle_FutureYearSelected</t>
-        </is>
-      </c>
-      <c r="E283" s="2" t="inlineStr"/>
-      <c r="F283" s="2" t="inlineStr"/>
-      <c r="G283" s="2" t="inlineStr"/>
-      <c r="H283" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="284">
-      <c r="A284" s="2" t="inlineStr">
-        <is>
-          <t>ERP.CRE/extensions/Zig365-Commercial-Real-Estate-Property-Management-Contracts-Tests/src/CreateOwnerStatementErrorMsgs.Codeunit.al</t>
-        </is>
-      </c>
-      <c r="B284" s="2" t="inlineStr">
-        <is>
-          <t>CreateOwnerStatementErrorMsgs</t>
-        </is>
-      </c>
-      <c r="C284" s="2" t="inlineStr">
-        <is>
-          <t>50119</t>
-        </is>
-      </c>
-      <c r="D284" s="2" t="inlineStr">
-        <is>
-          <t>CheckPeriodToSettle_NoPeriodSpecified</t>
-        </is>
-      </c>
-      <c r="E284" s="2" t="inlineStr"/>
-      <c r="F284" s="2" t="inlineStr"/>
-      <c r="G284" s="2" t="inlineStr"/>
-      <c r="H284" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="285">
-      <c r="A285" s="2" t="inlineStr">
-        <is>
-          <t>ERP.CRE/extensions/Zig365-Commercial-Real-Estate-Property-Management-Contracts-Tests/src/PropManContrLineElementTest.Codeunit.al</t>
-        </is>
-      </c>
-      <c r="B285" s="2" t="inlineStr">
-        <is>
-          <t>PropManContrLineElementTest</t>
-        </is>
-      </c>
-      <c r="C285" s="2" t="inlineStr">
-        <is>
-          <t>50105</t>
-        </is>
-      </c>
-      <c r="D285" s="2" t="inlineStr">
-        <is>
-          <t>WhenElementIsEmpty_ExpectError</t>
-        </is>
-      </c>
-      <c r="E285" s="2" t="inlineStr"/>
-      <c r="F285" s="2" t="inlineStr"/>
-      <c r="G285" s="2" t="inlineStr"/>
-      <c r="H285" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="286">
-      <c r="A286" s="2" t="inlineStr">
-        <is>
-          <t>ERP.CRE/extensions/Zig365-Commercial-Real-Estate-Property-Management-Contracts-Tests/src/PropManContrLineElementTest.Codeunit.al</t>
-        </is>
-      </c>
-      <c r="B286" s="2" t="inlineStr">
-        <is>
-          <t>PropManContrLineElementTest</t>
-        </is>
-      </c>
-      <c r="C286" s="2" t="inlineStr">
-        <is>
-          <t>50105</t>
-        </is>
-      </c>
-      <c r="D286" s="2" t="inlineStr">
-        <is>
-          <t>WhenPropManContrLineElementsAreCreated_CommissionAmountsAreCalculatedCorrectly</t>
-        </is>
-      </c>
-      <c r="E286" s="2" t="inlineStr"/>
-      <c r="F286" s="2" t="inlineStr"/>
-      <c r="G286" s="2" t="inlineStr"/>
-      <c r="H286" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="287">
-      <c r="A287" s="2" t="inlineStr">
-        <is>
-          <t>ERP.CRE/extensions/Zig365-Commercial-Real-Estate-Property-Management-Contracts-Tests/src/PropManContrLineElementTest.Codeunit.al</t>
-        </is>
-      </c>
-      <c r="B287" s="2" t="inlineStr">
-        <is>
-          <t>PropManContrLineElementTest</t>
-        </is>
-      </c>
-      <c r="C287" s="2" t="inlineStr">
-        <is>
-          <t>50105</t>
-        </is>
-      </c>
-      <c r="D287" s="2" t="inlineStr">
-        <is>
-          <t>WhenAddSelectedElements_ElementsAreAdded</t>
-        </is>
-      </c>
-      <c r="E287" s="2" t="inlineStr"/>
-      <c r="F287" s="2" t="inlineStr"/>
-      <c r="G287" s="2" t="inlineStr"/>
-      <c r="H287" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="288">
-      <c r="A288" s="2" t="inlineStr">
-        <is>
-          <t>ERP.CRE/extensions/Zig365-Commercial-Real-Estate-Property-Management-Contracts-Tests/src/PropManContractTest.Codeunit.al</t>
-        </is>
-      </c>
-      <c r="B288" s="2" t="inlineStr">
-        <is>
-          <t>PropManContractTest</t>
-        </is>
-      </c>
-      <c r="C288" s="2" t="inlineStr">
-        <is>
-          <t>50102</t>
-        </is>
-      </c>
-      <c r="D288" s="2" t="inlineStr">
-        <is>
-          <t>WhenNoSeriesIsSetup_NoIsCorrectlyRetrieved</t>
-        </is>
-      </c>
-      <c r="E288" s="2" t="inlineStr"/>
-      <c r="F288" s="2" t="inlineStr"/>
-      <c r="G288" s="2" t="inlineStr"/>
-      <c r="H288" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="289">
-      <c r="A289" s="2" t="inlineStr">
-        <is>
-          <t>ERP.CRE/extensions/Zig365-Commercial-Real-Estate-Property-Management-Contracts-Tests/src/PropManContractTest.Codeunit.al</t>
-        </is>
-      </c>
-      <c r="B289" s="2" t="inlineStr">
-        <is>
-          <t>PropManContractTest</t>
-        </is>
-      </c>
-      <c r="C289" s="2" t="inlineStr">
-        <is>
-          <t>50102</t>
-        </is>
-      </c>
-      <c r="D289" s="2" t="inlineStr">
-        <is>
-          <t>WhenRelatedSeriesIsUsed_NoIsCorrectlyRetrieved</t>
-        </is>
-      </c>
-      <c r="E289" s="2" t="inlineStr"/>
-      <c r="F289" s="2" t="inlineStr"/>
-      <c r="G289" s="2" t="inlineStr"/>
-      <c r="H289" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="290">
-      <c r="A290" s="2" t="inlineStr">
-        <is>
-          <t>ERP.CRE/extensions/Zig365-Commercial-Real-Estate-Property-Management-Contracts-Tests/src/PropManContractTest.Codeunit.al</t>
-        </is>
-      </c>
-      <c r="B290" s="2" t="inlineStr">
-        <is>
-          <t>PropManContractTest</t>
-        </is>
-      </c>
-      <c r="C290" s="2" t="inlineStr">
-        <is>
-          <t>50102</t>
-        </is>
-      </c>
-      <c r="D290" s="2" t="inlineStr">
-        <is>
-          <t>WhenSetupDoesNotExist_ExpectError</t>
-        </is>
-      </c>
-      <c r="E290" s="2" t="inlineStr"/>
-      <c r="F290" s="2" t="inlineStr"/>
-      <c r="G290" s="2" t="inlineStr"/>
-      <c r="H290" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="291">
-      <c r="A291" s="2" t="inlineStr">
-        <is>
-          <t>ERP.CRE/extensions/Zig365-Commercial-Real-Estate-Property-Management-Contracts-Tests/src/PropManContractTest.Codeunit.al</t>
-        </is>
-      </c>
-      <c r="B291" s="2" t="inlineStr">
-        <is>
-          <t>PropManContractTest</t>
-        </is>
-      </c>
-      <c r="C291" s="2" t="inlineStr">
-        <is>
-          <t>50102</t>
-        </is>
-      </c>
-      <c r="D291" s="2" t="inlineStr">
-        <is>
-          <t>WhenNoSeriesIsNotSetup_ExpectError</t>
-        </is>
-      </c>
-      <c r="E291" s="2" t="inlineStr"/>
-      <c r="F291" s="2" t="inlineStr"/>
-      <c r="G291" s="2" t="inlineStr"/>
-      <c r="H291" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="292">
-      <c r="A292" s="2" t="inlineStr">
-        <is>
-          <t>ERP.CRE/extensions/Zig365-Commercial-Real-Estate-Property-Management-Contracts-Tests/src/PropManContractTest.Codeunit.al</t>
-        </is>
-      </c>
-      <c r="B292" s="2" t="inlineStr">
-        <is>
-          <t>PropManContractTest</t>
-        </is>
-      </c>
-      <c r="C292" s="2" t="inlineStr">
-        <is>
-          <t>50102</t>
-        </is>
-      </c>
-      <c r="D292" s="2" t="inlineStr">
-        <is>
-          <t>WhenManualNosAreNotAccepted_ExpectError</t>
-        </is>
-      </c>
-      <c r="E292" s="2" t="inlineStr"/>
-      <c r="F292" s="2" t="inlineStr"/>
-      <c r="G292" s="2" t="inlineStr"/>
-      <c r="H292" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="293">
-      <c r="A293" s="2" t="inlineStr">
-        <is>
-          <t>ERP.CRE/extensions/Zig365-Commercial-Real-Estate-Property-Management-Contracts-Tests/src/PropManContractTest.Codeunit.al</t>
-        </is>
-      </c>
-      <c r="B293" s="2" t="inlineStr">
-        <is>
-          <t>PropManContractTest</t>
-        </is>
-      </c>
-      <c r="C293" s="2" t="inlineStr">
-        <is>
-          <t>50102</t>
-        </is>
-      </c>
-      <c r="D293" s="2" t="inlineStr">
-        <is>
-          <t>WhenManualNosAreAccepted_ExpectNoCanBeAssigned</t>
-        </is>
-      </c>
-      <c r="E293" s="2" t="inlineStr"/>
-      <c r="F293" s="2" t="inlineStr"/>
-      <c r="G293" s="2" t="inlineStr"/>
-      <c r="H293" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="294">
-      <c r="A294" s="2" t="inlineStr">
-        <is>
-          <t>ERP.CRE/extensions/Zig365-Commercial-Real-Estate-Property-Management-Contracts-Tests/src/PropManContractTest.Codeunit.al</t>
-        </is>
-      </c>
-      <c r="B294" s="2" t="inlineStr">
-        <is>
-          <t>PropManContractTest</t>
-        </is>
-      </c>
-      <c r="C294" s="2" t="inlineStr">
-        <is>
-          <t>50102</t>
-        </is>
-      </c>
-      <c r="D294" s="2" t="inlineStr">
-        <is>
-          <t>WhenContractIsDeleted_PropertyOwnersAreDeleted</t>
-        </is>
-      </c>
-      <c r="E294" s="2" t="inlineStr"/>
-      <c r="F294" s="2" t="inlineStr"/>
-      <c r="G294" s="2" t="inlineStr"/>
-      <c r="H294" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="295">
-      <c r="A295" s="2" t="inlineStr">
-        <is>
-          <t>ERP.CRE/extensions/Zig365-Commercial-Real-Estate-Property-Management-Contracts-Tests/src/PropManContractTest.Codeunit.al</t>
-        </is>
-      </c>
-      <c r="B295" s="2" t="inlineStr">
-        <is>
-          <t>PropManContractTest</t>
-        </is>
-      </c>
-      <c r="C295" s="2" t="inlineStr">
-        <is>
-          <t>50102</t>
-        </is>
-      </c>
-      <c r="D295" s="2" t="inlineStr">
-        <is>
-          <t>WhenContractIsDeleted_ContractLinesAreDeleted</t>
-        </is>
-      </c>
-      <c r="E295" s="2" t="inlineStr"/>
-      <c r="F295" s="2" t="inlineStr"/>
-      <c r="G295" s="2" t="inlineStr"/>
-      <c r="H295" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="296">
-      <c r="A296" s="2" t="inlineStr">
-        <is>
-          <t>ERP.CRE/extensions/Zig365-Commercial-Real-Estate-Property-Management-Contracts-Tests/src/PropManContractTest.Codeunit.al</t>
-        </is>
-      </c>
-      <c r="B296" s="2" t="inlineStr">
-        <is>
-          <t>PropManContractTest</t>
-        </is>
-      </c>
-      <c r="C296" s="2" t="inlineStr">
-        <is>
-          <t>50102</t>
-        </is>
-      </c>
-      <c r="D296" s="2" t="inlineStr">
-        <is>
-          <t>WhenClusterHasNotTheCorrectType_ExpectError</t>
-        </is>
-      </c>
-      <c r="E296" s="2" t="inlineStr"/>
-      <c r="F296" s="2" t="inlineStr"/>
-      <c r="G296" s="2" t="inlineStr"/>
-      <c r="H296" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="297">
-      <c r="A297" s="2" t="inlineStr">
-        <is>
-          <t>ERP.CRE/extensions/Zig365-Commercial-Real-Estate-Property-Management-Contracts-Tests/src/PropManContractTest.Codeunit.al</t>
-        </is>
-      </c>
-      <c r="B297" s="2" t="inlineStr">
-        <is>
-          <t>PropManContractTest</t>
-        </is>
-      </c>
-      <c r="C297" s="2" t="inlineStr">
-        <is>
-          <t>50102</t>
-        </is>
-      </c>
-      <c r="D297" s="2" t="inlineStr">
-        <is>
-          <t>WhenAddPropertyOwnerAndClusterIsEmpty_ExpectError</t>
-        </is>
-      </c>
-      <c r="E297" s="2" t="inlineStr"/>
-      <c r="F297" s="2" t="inlineStr"/>
-      <c r="G297" s="2" t="inlineStr"/>
-      <c r="H297" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="298">
-      <c r="A298" s="2" t="inlineStr">
-        <is>
-          <t>ERP.CRE/extensions/Zig365-Commercial-Real-Estate-Property-Management-Contracts-Tests/src/PropManContractTest.Codeunit.al</t>
-        </is>
-      </c>
-      <c r="B298" s="2" t="inlineStr">
-        <is>
-          <t>PropManContractTest</t>
-        </is>
-      </c>
-      <c r="C298" s="2" t="inlineStr">
-        <is>
-          <t>50102</t>
-        </is>
-      </c>
-      <c r="D298" s="2" t="inlineStr">
-        <is>
-          <t>WhenSetEndDateBeforeStartDate_ExpectError</t>
-        </is>
-      </c>
-      <c r="E298" s="2" t="inlineStr"/>
-      <c r="F298" s="2" t="inlineStr"/>
-      <c r="G298" s="2" t="inlineStr"/>
-      <c r="H298" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="299">
-      <c r="A299" s="2" t="inlineStr">
-        <is>
-          <t>ERP.CRE/extensions/Zig365-Commercial-Real-Estate-Property-Management-Contracts-Tests/src/PropManContractTest.Codeunit.al</t>
-        </is>
-      </c>
-      <c r="B299" s="2" t="inlineStr">
-        <is>
-          <t>PropManContractTest</t>
-        </is>
-      </c>
-      <c r="C299" s="2" t="inlineStr">
-        <is>
-          <t>50102</t>
-        </is>
-      </c>
-      <c r="D299" s="2" t="inlineStr">
-        <is>
-          <t>WhenSetStartDateAfterEndDate_ExpectError</t>
-        </is>
-      </c>
-      <c r="E299" s="2" t="inlineStr"/>
-      <c r="F299" s="2" t="inlineStr"/>
-      <c r="G299" s="2" t="inlineStr"/>
-      <c r="H299" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="300">
-      <c r="A300" s="2" t="inlineStr">
-        <is>
-          <t>ERP.CRE/extensions/Zig365-Commercial-Real-Estate-Property-Management-Contracts-Tests/src/PropManContractTest.Codeunit.al</t>
-        </is>
-      </c>
-      <c r="B300" s="2" t="inlineStr">
-        <is>
-          <t>PropManContractTest</t>
-        </is>
-      </c>
-      <c r="C300" s="2" t="inlineStr">
-        <is>
-          <t>50102</t>
-        </is>
-      </c>
-      <c r="D300" s="2" t="inlineStr">
-        <is>
-          <t>WhenSetStartDateAndClusterIsEmpty_ExpectError</t>
-        </is>
-      </c>
-      <c r="E300" s="2" t="inlineStr"/>
-      <c r="F300" s="2" t="inlineStr"/>
-      <c r="G300" s="2" t="inlineStr"/>
-      <c r="H300" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="301">
-      <c r="A301" s="2" t="inlineStr">
-        <is>
-          <t>ERP.CRE/extensions/Zig365-Commercial-Real-Estate-Property-Management-Contracts-Tests/src/PropManContractTest.Codeunit.al</t>
-        </is>
-      </c>
-      <c r="B301" s="2" t="inlineStr">
-        <is>
-          <t>PropManContractTest</t>
-        </is>
-      </c>
-      <c r="C301" s="2" t="inlineStr">
-        <is>
-          <t>50102</t>
-        </is>
-      </c>
-      <c r="D301" s="2" t="inlineStr">
-        <is>
-          <t>WhenSetStartDateAndContractLineWithLowerStartDateExists_ExpectError</t>
-        </is>
-      </c>
-      <c r="E301" s="2" t="inlineStr"/>
-      <c r="F301" s="2" t="inlineStr"/>
-      <c r="G301" s="2" t="inlineStr"/>
-      <c r="H301" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="302">
-      <c r="A302" s="2" t="inlineStr">
-        <is>
-          <t>ERP.CRE/extensions/Zig365-Commercial-Real-Estate-Property-Management-Contracts-Tests/src/PropManContractTest.Codeunit.al</t>
-        </is>
-      </c>
-      <c r="B302" s="2" t="inlineStr">
-        <is>
-          <t>PropManContractTest</t>
-        </is>
-      </c>
-      <c r="C302" s="2" t="inlineStr">
-        <is>
-          <t>50102</t>
-        </is>
-      </c>
-      <c r="D302" s="2" t="inlineStr">
-        <is>
-          <t>WhenClearStartDateAndContractLineExists_ExpectError</t>
-        </is>
-      </c>
-      <c r="E302" s="2" t="inlineStr"/>
-      <c r="F302" s="2" t="inlineStr"/>
-      <c r="G302" s="2" t="inlineStr"/>
-      <c r="H302" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="303">
-      <c r="A303" s="2" t="inlineStr">
-        <is>
-          <t>ERP.CRE/extensions/Zig365-Commercial-Real-Estate-Property-Management-Contracts-Tests/src/PropManContractTest.Codeunit.al</t>
-        </is>
-      </c>
-      <c r="B303" s="2" t="inlineStr">
-        <is>
-          <t>PropManContractTest</t>
-        </is>
-      </c>
-      <c r="C303" s="2" t="inlineStr">
-        <is>
-          <t>50102</t>
-        </is>
-      </c>
-      <c r="D303" s="2" t="inlineStr">
-        <is>
-          <t>WhenSetStartDateAndPreviousContractLineOverlappingExists_ExpectError</t>
-        </is>
-      </c>
-      <c r="E303" s="2" t="inlineStr"/>
-      <c r="F303" s="2" t="inlineStr"/>
-      <c r="G303" s="2" t="inlineStr"/>
-      <c r="H303" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="304">
-      <c r="A304" s="2" t="inlineStr">
-        <is>
-          <t>ERP.CRE/extensions/Zig365-Commercial-Real-Estate-Property-Management-Contracts-Tests/src/PropManContractTest.Codeunit.al</t>
-        </is>
-      </c>
-      <c r="B304" s="2" t="inlineStr">
-        <is>
-          <t>PropManContractTest</t>
-        </is>
-      </c>
-      <c r="C304" s="2" t="inlineStr">
-        <is>
-          <t>50102</t>
-        </is>
-      </c>
-      <c r="D304" s="2" t="inlineStr">
-        <is>
-          <t>WhenSetStartDateOnLineWithEndDateAndFutureContractLineOverlappingExists_ExpectError</t>
-        </is>
-      </c>
-      <c r="E304" s="2" t="inlineStr"/>
-      <c r="F304" s="2" t="inlineStr"/>
-      <c r="G304" s="2" t="inlineStr"/>
-      <c r="H304" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="305">
-      <c r="A305" s="2" t="inlineStr">
-        <is>
-          <t>ERP.CRE/extensions/Zig365-Commercial-Real-Estate-Property-Management-Contracts-Tests/src/PropManContractTest.Codeunit.al</t>
-        </is>
-      </c>
-      <c r="B305" s="2" t="inlineStr">
-        <is>
-          <t>PropManContractTest</t>
-        </is>
-      </c>
-      <c r="C305" s="2" t="inlineStr">
-        <is>
-          <t>50102</t>
-        </is>
-      </c>
-      <c r="D305" s="2" t="inlineStr">
-        <is>
-          <t>WhenSetStartDateOnLineWithEmptyEndDateAndFutureContractLineOverlappingExists_ExpectError</t>
-        </is>
-      </c>
-      <c r="E305" s="2" t="inlineStr"/>
-      <c r="F305" s="2" t="inlineStr"/>
-      <c r="G305" s="2" t="inlineStr"/>
-      <c r="H305" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="306">
-      <c r="A306" s="2" t="inlineStr">
-        <is>
-          <t>ERP.CRE/extensions/Zig365-Commercial-Real-Estate-Property-Management-Contracts-Tests/src/PropManContractTest.Codeunit.al</t>
-        </is>
-      </c>
-      <c r="B306" s="2" t="inlineStr">
-        <is>
-          <t>PropManContractTest</t>
-        </is>
-      </c>
-      <c r="C306" s="2" t="inlineStr">
-        <is>
-          <t>50102</t>
-        </is>
-      </c>
-      <c r="D306" s="2" t="inlineStr">
-        <is>
-          <t>WhenSetEndDateReceivingsExistAfterEndDate_ExpectError</t>
-        </is>
-      </c>
-      <c r="E306" s="2" t="inlineStr"/>
-      <c r="F306" s="2" t="inlineStr"/>
-      <c r="G306" s="2" t="inlineStr"/>
-      <c r="H306" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="307">
-      <c r="A307" s="2" t="inlineStr">
-        <is>
-          <t>ERP.CRE/extensions/Zig365-Commercial-Real-Estate-Property-Management-Contracts-Tests/src/PropManContractTest.Codeunit.al</t>
-        </is>
-      </c>
-      <c r="B307" s="2" t="inlineStr">
-        <is>
-          <t>PropManContractTest</t>
-        </is>
-      </c>
-      <c r="C307" s="2" t="inlineStr">
-        <is>
-          <t>50102</t>
-        </is>
-      </c>
-      <c r="D307" s="2" t="inlineStr">
-        <is>
-          <t>WhenEndContractAndContractLineWithNewerStartDateExist_ExpectError</t>
-        </is>
-      </c>
-      <c r="E307" s="2" t="inlineStr"/>
-      <c r="F307" s="2" t="inlineStr"/>
-      <c r="G307" s="2" t="inlineStr"/>
-      <c r="H307" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="308">
-      <c r="A308" s="2" t="inlineStr">
-        <is>
-          <t>ERP.CRE/extensions/Zig365-Commercial-Real-Estate-Property-Management-Contracts-Tests/src/PropManContractTest.Codeunit.al</t>
-        </is>
-      </c>
-      <c r="B308" s="2" t="inlineStr">
-        <is>
-          <t>PropManContractTest</t>
-        </is>
-      </c>
-      <c r="C308" s="2" t="inlineStr">
-        <is>
-          <t>50102</t>
-        </is>
-      </c>
-      <c r="D308" s="2" t="inlineStr">
-        <is>
-          <t>WhenChangeExistingEndDateToNonEmptyValueAndOverlappingContractExists_ExpectError</t>
-        </is>
-      </c>
-      <c r="E308" s="2" t="inlineStr"/>
-      <c r="F308" s="2" t="inlineStr"/>
-      <c r="G308" s="2" t="inlineStr"/>
-      <c r="H308" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="309">
-      <c r="A309" s="2" t="inlineStr">
-        <is>
-          <t>ERP.CRE/extensions/Zig365-Commercial-Real-Estate-Property-Management-Contracts-Tests/src/PropManContractTest.Codeunit.al</t>
-        </is>
-      </c>
-      <c r="B309" s="2" t="inlineStr">
-        <is>
-          <t>PropManContractTest</t>
-        </is>
-      </c>
-      <c r="C309" s="2" t="inlineStr">
-        <is>
-          <t>50102</t>
-        </is>
-      </c>
-      <c r="D309" s="2" t="inlineStr">
-        <is>
-          <t>WhenChangeExistingEndDateToEmptyValueAndOverlappingContractExists_ExpectError</t>
-        </is>
-      </c>
-      <c r="E309" s="2" t="inlineStr"/>
-      <c r="F309" s="2" t="inlineStr"/>
-      <c r="G309" s="2" t="inlineStr"/>
-      <c r="H309" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="310">
-      <c r="A310" s="2" t="inlineStr">
-        <is>
-          <t>ERP.CRE/extensions/Zig365-Commercial-Real-Estate-Property-Management-Contracts-Tests/src/PropManContractTest.Codeunit.al</t>
-        </is>
-      </c>
-      <c r="B310" s="2" t="inlineStr">
-        <is>
-          <t>PropManContractTest</t>
-        </is>
-      </c>
-      <c r="C310" s="2" t="inlineStr">
-        <is>
-          <t>50102</t>
-        </is>
-      </c>
-      <c r="D310" s="2" t="inlineStr">
-        <is>
-          <t>WhenContractIsEnded_ExpectEndDateOnContractLineIsUpdated</t>
-        </is>
-      </c>
-      <c r="E310" s="2" t="inlineStr"/>
-      <c r="F310" s="2" t="inlineStr"/>
-      <c r="G310" s="2" t="inlineStr"/>
-      <c r="H310" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="311">
-      <c r="A311" s="2" t="inlineStr">
-        <is>
-          <t>ERP.CRE/extensions/Zig365-Commercial-Real-Estate-Property-Management-Contracts-Tests/src/ReceivingsEntryTest.Codeunit.al</t>
-        </is>
-      </c>
-      <c r="B311" s="2" t="inlineStr">
-        <is>
-          <t>ReceivingsEntryTest</t>
-        </is>
-      </c>
-      <c r="C311" s="2" t="inlineStr">
-        <is>
-          <t>50112</t>
-        </is>
-      </c>
-      <c r="D311" s="2" t="inlineStr">
-        <is>
-          <t>WhenNoContractLineActive_ExpectConcerningProlRunError</t>
-        </is>
-      </c>
-      <c r="E311" s="2" t="inlineStr"/>
-      <c r="F311" s="2" t="inlineStr"/>
-      <c r="G311" s="2" t="inlineStr"/>
-      <c r="H311" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="312">
-      <c r="A312" s="2" t="inlineStr">
-        <is>
-          <t>ERP.CRE/extensions/Zig365-Commercial-Real-Estate-Property-Management-Contracts-Tests/src/ReceivingsEntryTest.Codeunit.al</t>
-        </is>
-      </c>
-      <c r="B312" s="2" t="inlineStr">
-        <is>
-          <t>ReceivingsEntryTest</t>
-        </is>
-      </c>
-      <c r="C312" s="2" t="inlineStr">
-        <is>
-          <t>50112</t>
-        </is>
-      </c>
-      <c r="D312" s="2" t="inlineStr">
-        <is>
-          <t>WhenNoContractLineElementRecorded_ExpectConcerningProlRunError</t>
-        </is>
-      </c>
-      <c r="E312" s="2" t="inlineStr"/>
-      <c r="F312" s="2" t="inlineStr"/>
-      <c r="G312" s="2" t="inlineStr"/>
-      <c r="H312" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="313">
-      <c r="A313" s="2" t="inlineStr">
-        <is>
-          <t>ERP.CRE/extensions/Zig365-Commercial-Real-Estate-Property-Management-Contracts-Tests/src/ReceivingsEntryTest.Codeunit.al</t>
-        </is>
-      </c>
-      <c r="B313" s="2" t="inlineStr">
-        <is>
-          <t>ReceivingsEntryTest</t>
-        </is>
-      </c>
-      <c r="C313" s="2" t="inlineStr">
-        <is>
-          <t>50112</t>
-        </is>
-      </c>
-      <c r="D313" s="2" t="inlineStr">
-        <is>
-          <t>WhenPMBlanketContractLineActive_ExpectContractNoUpdatedInReceivingsEntryAndRentalContract</t>
-        </is>
-      </c>
-      <c r="E313" s="2" t="inlineStr"/>
-      <c r="F313" s="2" t="inlineStr"/>
-      <c r="G313" s="2" t="inlineStr"/>
-      <c r="H313" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="314">
-      <c r="A314" s="2" t="inlineStr">
-        <is>
-          <t>ERP.CRE/extensions/Zig365-Commercial-Real-Estate-Property-Management-Contracts-Tests/src/ReceivingsEntryTest.Codeunit.al</t>
-        </is>
-      </c>
-      <c r="B314" s="2" t="inlineStr">
-        <is>
-          <t>ReceivingsEntryTest</t>
-        </is>
-      </c>
-      <c r="C314" s="2" t="inlineStr">
-        <is>
-          <t>50112</t>
-        </is>
-      </c>
-      <c r="D314" s="2" t="inlineStr">
-        <is>
-          <t>WhenPostingRentalInvoice_ExpectContractNoUpdatedInReceivingsEntry</t>
-        </is>
-      </c>
-      <c r="E314" s="2" t="inlineStr"/>
-      <c r="F314" s="2" t="inlineStr"/>
-      <c r="G314" s="2" t="inlineStr"/>
-      <c r="H314" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="315">
-      <c r="A315" s="2" t="inlineStr">
-        <is>
-          <t>ERP.CRE/extensions/Zig365-Commercial-Real-Estate-Property-Management-Contracts-Tests/src/ReceivingsEntryTest.Codeunit.al</t>
-        </is>
-      </c>
-      <c r="B315" s="2" t="inlineStr">
-        <is>
-          <t>ReceivingsEntryTest</t>
-        </is>
-      </c>
-      <c r="C315" s="2" t="inlineStr">
-        <is>
-          <t>50112</t>
-        </is>
-      </c>
-      <c r="D315" s="2" t="inlineStr">
-        <is>
-          <t>WhenPostingRentalInvoiceAndNoContractLineActive_ExpectConcerningError</t>
-        </is>
-      </c>
-      <c r="E315" s="2" t="inlineStr"/>
-      <c r="F315" s="2" t="inlineStr"/>
-      <c r="G315" s="2" t="inlineStr"/>
-      <c r="H315" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="316">
-      <c r="A316" s="2" t="inlineStr">
-        <is>
-          <t>ERP.CRE/extensions/Zig365-Commercial-Real-Estate-Property-Management-Contracts-Tests/src/ReceivingsEntryTest.Codeunit.al</t>
-        </is>
-      </c>
-      <c r="B316" s="2" t="inlineStr">
-        <is>
-          <t>ReceivingsEntryTest</t>
-        </is>
-      </c>
-      <c r="C316" s="2" t="inlineStr">
-        <is>
-          <t>50112</t>
-        </is>
-      </c>
-      <c r="D316" s="2" t="inlineStr">
-        <is>
-          <t>WhenPostingRentalInvoiceAndNoContractLineElementRecorded_ExpectConcerningError</t>
-        </is>
-      </c>
-      <c r="E316" s="2" t="inlineStr"/>
-      <c r="F316" s="2" t="inlineStr"/>
-      <c r="G316" s="2" t="inlineStr"/>
-      <c r="H316" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="317">
-      <c r="A317" s="2" t="inlineStr">
-        <is>
-          <t>ERP.CRE/extensions/Zig365-Commercial-Real-Estate-Property-Management-Contracts-Tests/src/ReceivingsEntryTest.Codeunit.al</t>
-        </is>
-      </c>
-      <c r="B317" s="2" t="inlineStr">
-        <is>
-          <t>ReceivingsEntryTest</t>
-        </is>
-      </c>
-      <c r="C317" s="2" t="inlineStr">
-        <is>
-          <t>50112</t>
-        </is>
-      </c>
-      <c r="D317" s="2" t="inlineStr">
-        <is>
-          <t>WhenPropManContractLineActive_ExpectContractNoUpdatedInRentalContract</t>
-        </is>
-      </c>
-      <c r="E317" s="2" t="inlineStr"/>
-      <c r="F317" s="2" t="inlineStr"/>
-      <c r="G317" s="2" t="inlineStr"/>
-      <c r="H317" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="318">
-      <c r="A318" s="2" t="inlineStr">
-        <is>
-          <t>ERP.CRE/extensions/Zig365-Commercial-Real-Estate-Foundation-Tests/src/CommercialRealEstateSetupTest.Codeunit.al</t>
-        </is>
-      </c>
-      <c r="B318" s="2" t="inlineStr">
-        <is>
-          <t>CommercialRealEstateSetupTest</t>
-        </is>
-      </c>
-      <c r="C318" s="2" t="inlineStr">
-        <is>
-          <t>50300</t>
-        </is>
-      </c>
-      <c r="D318" s="2" t="inlineStr">
-        <is>
-          <t>TestInitializeSetupWhenSetupDoesNotExist</t>
-        </is>
-      </c>
-      <c r="E318" s="2" t="inlineStr"/>
-      <c r="F318" s="2" t="inlineStr"/>
-      <c r="G318" s="2" t="inlineStr"/>
-      <c r="H318" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="319">
-      <c r="A319" s="2" t="inlineStr">
-        <is>
-          <t>ERP.CRE/extensions/Zig365-Commercial-Real-Estate-Foundation-Tests/src/CommercialRealEstateSetupTest.Codeunit.al</t>
-        </is>
-      </c>
-      <c r="B319" s="2" t="inlineStr">
-        <is>
-          <t>CommercialRealEstateSetupTest</t>
-        </is>
-      </c>
-      <c r="C319" s="2" t="inlineStr">
-        <is>
-          <t>50300</t>
-        </is>
-      </c>
-      <c r="D319" s="2" t="inlineStr">
-        <is>
-          <t>TestInitializeSetupWhenSetupExists</t>
-        </is>
-      </c>
-      <c r="E319" s="2" t="inlineStr"/>
-      <c r="F319" s="2" t="inlineStr"/>
-      <c r="G319" s="2" t="inlineStr"/>
-      <c r="H319" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="320">
-      <c r="A320" s="2" t="inlineStr">
-        <is>
-          <t>ERP.CRE/extensions/Zig365-Commercial-Real-Estate-Foundation-Tests/src/CREBankAccountTest.Codeunit.al</t>
-        </is>
-      </c>
-      <c r="B320" s="2" t="inlineStr">
-        <is>
-          <t>CRE Bank Account Test</t>
-        </is>
-      </c>
-      <c r="C320" s="2" t="inlineStr">
-        <is>
-          <t>50302</t>
-        </is>
-      </c>
-      <c r="D320" s="2" t="inlineStr">
-        <is>
-          <t>WhenContactNoOnBankAccountIsValidated_VerifyAccountHolderDetailsAreCorrect</t>
-        </is>
-      </c>
-      <c r="E320" s="2" t="inlineStr"/>
-      <c r="F320" s="2" t="inlineStr"/>
-      <c r="G320" s="2" t="inlineStr"/>
-      <c r="H320" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="321">
-      <c r="A321" s="2" t="inlineStr">
-        <is>
-          <t>ERP.CRE/extensions/Zig365-Commercial-Real-Estate-Foundation-Tests/src/CREBankAccountTest.Codeunit.al</t>
-        </is>
-      </c>
-      <c r="B321" s="2" t="inlineStr">
-        <is>
-          <t>CRE Bank Account Test</t>
-        </is>
-      </c>
-      <c r="C321" s="2" t="inlineStr">
-        <is>
-          <t>50302</t>
-        </is>
-      </c>
-      <c r="D321" s="2" t="inlineStr">
-        <is>
-          <t>WhenContactNoOnBankAccountIsValidated_VerifyAccountHolderDetailsAreCorrectWhenBlanked</t>
-        </is>
-      </c>
-      <c r="E321" s="2" t="inlineStr"/>
-      <c r="F321" s="2" t="inlineStr"/>
-      <c r="G321" s="2" t="inlineStr"/>
-      <c r="H321" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="322">
-      <c r="A322" s="2" t="inlineStr">
-        <is>
-          <t>ERP.CRE/extensions/Zig365-Commercial-Real-Estate-Foundation-Tests/src/CREBankAccountTest.Codeunit.al</t>
-        </is>
-      </c>
-      <c r="B322" s="2" t="inlineStr">
-        <is>
-          <t>CRE Bank Account Test</t>
-        </is>
-      </c>
-      <c r="C322" s="2" t="inlineStr">
-        <is>
-          <t>50302</t>
-        </is>
-      </c>
-      <c r="D322" s="2" t="inlineStr">
-        <is>
-          <t>WhenContactNoOnBankAccountIsValidated_VerifyAccountHolderDetailsAreCorrectWhenValueIsUnchanged</t>
-        </is>
-      </c>
-      <c r="E322" s="2" t="inlineStr"/>
-      <c r="F322" s="2" t="inlineStr"/>
-      <c r="G322" s="2" t="inlineStr"/>
-      <c r="H322" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="323">
-      <c r="A323" s="2" t="inlineStr">
-        <is>
-          <t>ERP.CRE/extensions/Zig365-Commercial-Real-Estate-Foundation-Tests/src/DateFormulaHelperTest.Codeunit.al</t>
-        </is>
-      </c>
-      <c r="B323" s="2" t="inlineStr">
-        <is>
-          <t>DateFormulaHelperTest</t>
-        </is>
-      </c>
-      <c r="C323" s="2" t="inlineStr">
-        <is>
-          <t>50301</t>
-        </is>
-      </c>
-      <c r="D323" s="2" t="inlineStr">
-        <is>
-          <t>WhenDateFormulaContainsNumbers_ExpectValueAccepted</t>
-        </is>
-      </c>
-      <c r="E323" s="2" t="inlineStr"/>
-      <c r="F323" s="2" t="inlineStr"/>
-      <c r="G323" s="2" t="inlineStr"/>
-      <c r="H323" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="324">
-      <c r="A324" s="2" t="inlineStr">
-        <is>
-          <t>ERP.CRE/extensions/Zig365-Commercial-Real-Estate-Foundation-Tests/src/DateFormulaHelperTest.Codeunit.al</t>
-        </is>
-      </c>
-      <c r="B324" s="2" t="inlineStr">
-        <is>
-          <t>DateFormulaHelperTest</t>
-        </is>
-      </c>
-      <c r="C324" s="2" t="inlineStr">
-        <is>
-          <t>50301</t>
-        </is>
-      </c>
-      <c r="D324" s="2" t="inlineStr">
-        <is>
-          <t>WhenDateFormulaDoesNotContainNumbers_ExpectError</t>
-        </is>
-      </c>
-      <c r="E324" s="2" t="inlineStr"/>
-      <c r="F324" s="2" t="inlineStr"/>
-      <c r="G324" s="2" t="inlineStr"/>
-      <c r="H324" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="H182" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H324"/>
+  <autoFilter ref="A1:H182"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -10260,7 +6000,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D26"/>
+  <dimension ref="A1:D27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -10294,14 +6034,14 @@
     <row r="2">
       <c r="A2" s="6" t="inlineStr">
         <is>
-          <t>PropManContractTest</t>
+          <t>ElementCheckTest</t>
         </is>
       </c>
       <c r="B2" s="7" t="n">
-        <v>50102</v>
+        <v>50128</v>
       </c>
       <c r="C2" s="7" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="D2" s="8" t="inlineStr">
         <is>
@@ -10312,14 +6052,14 @@
     <row r="3">
       <c r="A3" s="6" t="inlineStr">
         <is>
-          <t>PMBlanketContractLineTest</t>
+          <t>PropManContractTest</t>
         </is>
       </c>
       <c r="B3" s="7" t="n">
-        <v>50101</v>
+        <v>50102</v>
       </c>
       <c r="C3" s="7" t="n">
-        <v>42</v>
+        <v>23</v>
       </c>
       <c r="D3" s="8" t="inlineStr">
         <is>
@@ -10330,14 +6070,14 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>ExpensesEntryTest</t>
+          <t>PMBlanketContractLineTest</t>
         </is>
       </c>
       <c r="B4" s="7" t="n">
-        <v>50114</v>
+        <v>50101</v>
       </c>
       <c r="C4" s="7" t="n">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="D4" s="8" t="inlineStr">
         <is>
@@ -10348,14 +6088,14 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>PropManContractLineTest</t>
+          <t>ExpensesEntryTest</t>
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>50100</v>
+        <v>50114</v>
       </c>
       <c r="C5" s="7" t="n">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="D5" s="8" t="inlineStr">
         <is>
@@ -10366,14 +6106,14 @@
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>ElementCheckTest</t>
+          <t>PropManContractLineTest</t>
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>50128</v>
+        <v>50100</v>
       </c>
       <c r="C6" s="7" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="D6" s="8" t="inlineStr">
         <is>
@@ -10391,7 +6131,7 @@
         <v>50104</v>
       </c>
       <c r="C7" s="7" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="D7" s="8" t="inlineStr">
         <is>
@@ -10409,7 +6149,7 @@
         <v>50127</v>
       </c>
       <c r="C8" s="7" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="D8" s="8" t="inlineStr">
         <is>
@@ -10427,7 +6167,7 @@
         <v>50123</v>
       </c>
       <c r="C9" s="7" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="D9" s="8" t="inlineStr">
         <is>
@@ -10445,7 +6185,7 @@
         <v>50117</v>
       </c>
       <c r="C10" s="7" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="D10" s="9" t="inlineStr">
         <is>
@@ -10463,7 +6203,7 @@
         <v>50112</v>
       </c>
       <c r="C11" s="7" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="D11" s="8" t="inlineStr">
         <is>
@@ -10481,7 +6221,7 @@
         <v>50111</v>
       </c>
       <c r="C12" s="7" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D12" s="8" t="inlineStr">
         <is>
@@ -10492,32 +6232,32 @@
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>CRE Bank Account Test</t>
+          <t>RentBrokerageParameterTest</t>
         </is>
       </c>
       <c r="B13" s="7" t="n">
-        <v>50302</v>
+        <v>50108</v>
       </c>
       <c r="C13" s="7" t="n">
-        <v>6</v>
-      </c>
-      <c r="D13" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
+        <v>5</v>
+      </c>
+      <c r="D13" s="8" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>PMBlanketContrLineElementTest</t>
+          <t>AlternateCostCodeTest</t>
         </is>
       </c>
       <c r="B14" s="7" t="n">
-        <v>50107</v>
+        <v>50113</v>
       </c>
       <c r="C14" s="7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D14" s="8" t="inlineStr">
         <is>
@@ -10528,32 +6268,32 @@
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>CreateOwnerStatementErrorMsgs</t>
+          <t>CRE Bank Account Test</t>
         </is>
       </c>
       <c r="B15" s="7" t="n">
-        <v>50119</v>
+        <v>50302</v>
       </c>
       <c r="C15" s="7" t="n">
-        <v>6</v>
-      </c>
-      <c r="D15" s="8" t="inlineStr">
-        <is>
-          <t>Yes</t>
+        <v>3</v>
+      </c>
+      <c r="D15" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>PropManContrLineElementTest</t>
+          <t>PMBlanketContrLineElementTest</t>
         </is>
       </c>
       <c r="B16" s="7" t="n">
-        <v>50105</v>
+        <v>50107</v>
       </c>
       <c r="C16" s="7" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D16" s="8" t="inlineStr">
         <is>
@@ -10564,14 +6304,14 @@
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>CommercialRealEstateSetupTest</t>
+          <t>CreateOwnerStatementErrorMsgs</t>
         </is>
       </c>
       <c r="B17" s="7" t="n">
-        <v>50300</v>
+        <v>50119</v>
       </c>
       <c r="C17" s="7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D17" s="8" t="inlineStr">
         <is>
@@ -10582,32 +6322,32 @@
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>DateFormulaHelperTest</t>
+          <t>PropManContrLineElementTest</t>
         </is>
       </c>
       <c r="B18" s="7" t="n">
-        <v>50301</v>
+        <v>50105</v>
       </c>
       <c r="C18" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="D18" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
+        <v>3</v>
+      </c>
+      <c r="D18" s="8" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>CreatePropManContractTest</t>
+          <t>CommercialRealEstateSetupTest</t>
         </is>
       </c>
       <c r="B19" s="7" t="n">
-        <v>50110</v>
+        <v>50300</v>
       </c>
       <c r="C19" s="7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D19" s="8" t="inlineStr">
         <is>
@@ -10618,32 +6358,32 @@
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>ContractLineRentBrokerageTest</t>
+          <t>DateFormulaHelperTest</t>
         </is>
       </c>
       <c r="B20" s="7" t="n">
-        <v>50106</v>
+        <v>50301</v>
       </c>
       <c r="C20" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="D20" s="8" t="inlineStr">
-        <is>
-          <t>Yes</t>
+        <v>2</v>
+      </c>
+      <c r="D20" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>BlankCtrLineRentBrokerageTest</t>
+          <t>CreatePropManContractTest</t>
         </is>
       </c>
       <c r="B21" s="7" t="n">
-        <v>50109</v>
+        <v>50110</v>
       </c>
       <c r="C21" s="7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D21" s="8" t="inlineStr">
         <is>
@@ -10654,14 +6394,14 @@
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>PropertyOwnerHistoryTest</t>
+          <t>ContractLineRentBrokerageTest</t>
         </is>
       </c>
       <c r="B22" s="7" t="n">
-        <v>50118</v>
+        <v>50106</v>
       </c>
       <c r="C22" s="7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D22" s="8" t="inlineStr">
         <is>
@@ -10672,14 +6412,14 @@
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>AlternateCostCodeTest</t>
+          <t>BlankCtrLineRentBrokerageTest</t>
         </is>
       </c>
       <c r="B23" s="7" t="n">
-        <v>50113</v>
+        <v>50109</v>
       </c>
       <c r="C23" s="7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D23" s="8" t="inlineStr">
         <is>
@@ -10690,14 +6430,14 @@
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>ContractLineCostCodeTest</t>
+          <t>PropertyOwnerHistoryTest</t>
         </is>
       </c>
       <c r="B24" s="7" t="n">
-        <v>50126</v>
+        <v>50118</v>
       </c>
       <c r="C24" s="7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D24" s="8" t="inlineStr">
         <is>
@@ -10708,11 +6448,11 @@
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>CommissionCalculationTest</t>
+          <t>ContractLineCostCodeTest</t>
         </is>
       </c>
       <c r="B25" s="7" t="n">
-        <v>50121</v>
+        <v>50126</v>
       </c>
       <c r="C25" s="7" t="n">
         <v>2</v>
@@ -10724,18 +6464,36 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="10" t="inlineStr">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>CommissionCalculationTest</t>
+        </is>
+      </c>
+      <c r="B26" s="7" t="n">
+        <v>50121</v>
+      </c>
+      <c r="C26" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" s="8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="10" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B26" s="11" t="inlineStr"/>
-      <c r="C26" s="11" t="n">
-        <v>323</v>
-      </c>
-      <c r="D26" s="11" t="inlineStr">
-        <is>
-          <t>299 PM / 24 Non-PM</t>
+      <c r="B27" s="11" t="inlineStr"/>
+      <c r="C27" s="11" t="n">
+        <v>181</v>
+      </c>
+      <c r="D27" s="11" t="inlineStr">
+        <is>
+          <t>169 PM / 12 Non-PM</t>
         </is>
       </c>
     </row>
@@ -10765,7 +6523,7 @@
       </c>
       <c r="B1" s="13" t="inlineStr">
         <is>
-          <t>2026-04-09 17:37</t>
+          <t>2026-04-16 22:56</t>
         </is>
       </c>
     </row>
@@ -10788,7 +6546,7 @@
         </is>
       </c>
       <c r="B3" s="13" t="n">
-        <v>47</v>
+        <v>25</v>
       </c>
     </row>
     <row r="4">
@@ -10798,7 +6556,7 @@
         </is>
       </c>
       <c r="B4" s="13" t="n">
-        <v>323</v>
+        <v>181</v>
       </c>
     </row>
     <row r="5">
@@ -10808,7 +6566,7 @@
         </is>
       </c>
       <c r="B5" s="13" t="n">
-        <v>299</v>
+        <v>169</v>
       </c>
     </row>
     <row r="6">
@@ -10818,7 +6576,7 @@
         </is>
       </c>
       <c r="B6" s="13" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7">
